--- a/mapping study graphs/outputs/mahalanobis_greedy_vs_hungarian/tables/mahalanobis_greedy_vs_hungarian_tables.xlsx
+++ b/mapping study graphs/outputs/mahalanobis_greedy_vs_hungarian/tables/mahalanobis_greedy_vs_hungarian_tables.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unit_level" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dataset_level" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="generator_level" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="paired_tests" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="skipped_units" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="meta" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="unit_level" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="dataset_level" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="generator_level" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="paired_tests" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="skipped_units" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="meta" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,13 +22,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -39,7 +42,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -47,12 +50,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -418,71 +430,71 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M107"/>
+  <dimension ref="A1:M121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Dataset</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Generator</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>GeneratorLabel</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Greedy_Mahalanobis</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Hungarian_Mahalanobis</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Diff_Hung_minus_Greedy</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>RelPct_Hung_minus_Greedy</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>RelPct_Unstable</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Direction</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Num_Matches</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Runtime_Greedy</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Runtime_Hungarian</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Runtime_Note</t>
         </is>
@@ -552,16 +564,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>32.553191</v>
+        <v>44.110818</v>
       </c>
       <c r="E3" t="n">
-        <v>10.038234</v>
+        <v>43.786276</v>
       </c>
       <c r="F3" t="n">
-        <v>-22.514957</v>
+        <v>-0.324542000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>-69.16359443840697</v>
+        <v>-0.7357424203740701</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
@@ -599,23 +611,23 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.969295</v>
+        <v>6.494969</v>
       </c>
       <c r="E4" t="n">
-        <v>3.102918</v>
+        <v>6.265554</v>
       </c>
       <c r="F4" t="n">
-        <v>1.133623</v>
+        <v>-0.2294150000000004</v>
       </c>
       <c r="G4" t="n">
-        <v>57.56491536311217</v>
+        <v>-3.532195457745839</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Hungarian worse (higher distance)</t>
+          <t>Hungarian better (lower distance)</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -740,16 +752,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>56.891797</v>
+        <v>110.861512</v>
       </c>
       <c r="E7" t="n">
-        <v>27.692581</v>
+        <v>110.561526</v>
       </c>
       <c r="F7" t="n">
-        <v>-29.199216</v>
+        <v>-0.2999860000000041</v>
       </c>
       <c r="G7" t="n">
-        <v>-51.32412322992715</v>
+        <v>-0.2705952630341214</v>
       </c>
       <c r="H7" t="b">
         <v>0</v>
@@ -834,16 +846,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>64.83434200000001</v>
+        <v>134.275819</v>
       </c>
       <c r="E9" t="n">
-        <v>26.091745</v>
+        <v>133.996058</v>
       </c>
       <c r="F9" t="n">
-        <v>-38.742597</v>
+        <v>-0.2797610000000077</v>
       </c>
       <c r="G9" t="n">
-        <v>-59.75628934431077</v>
+        <v>-0.2083480123848715</v>
       </c>
       <c r="H9" t="b">
         <v>0</v>
@@ -1351,23 +1363,23 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1.620219</v>
+        <v>5.795991</v>
       </c>
       <c r="E20" t="n">
-        <v>2.425423</v>
+        <v>5.65728</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8052039999999998</v>
+        <v>-0.1387109999999998</v>
       </c>
       <c r="G20" t="n">
-        <v>49.69723228773393</v>
+        <v>-2.393223177882778</v>
       </c>
       <c r="H20" t="b">
         <v>0</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Hungarian worse (higher distance)</t>
+          <t>Hungarian better (lower distance)</t>
         </is>
       </c>
       <c r="J20" t="n">
@@ -1586,16 +1598,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1.395532</v>
+        <v>2.101094</v>
       </c>
       <c r="E25" t="n">
-        <v>0.713123</v>
+        <v>1.888801</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.682409</v>
+        <v>-0.2122929999999998</v>
       </c>
       <c r="G25" t="n">
-        <v>-48.89955945116272</v>
+        <v>-10.10392681146107</v>
       </c>
       <c r="H25" t="b">
         <v>0</v>
@@ -2047,25 +2059,25 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>WGAN_GP</t>
+          <t>TVAE</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>WGAN-GP</t>
+          <t>TVAE</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>2.2412</v>
+        <v>1.251366</v>
       </c>
       <c r="E35" t="n">
-        <v>2.0781</v>
+        <v>1.065509</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.1631</v>
+        <v>-0.1858569999999999</v>
       </c>
       <c r="G35" t="n">
-        <v>-7.277351418882742</v>
+        <v>-14.85232937445959</v>
       </c>
       <c r="H35" t="b">
         <v>0</v>
@@ -2076,7 +2088,7 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
@@ -2094,25 +2106,25 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CTABGAN</t>
+          <t>GaussianCopula</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CTAB-GAN+</t>
+          <t>Gaussian Copula</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1.3445</v>
+        <v>1.911779</v>
       </c>
       <c r="E36" t="n">
-        <v>1.1716</v>
+        <v>1.536039</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.1729000000000001</v>
+        <v>-0.37574</v>
       </c>
       <c r="G36" t="n">
-        <v>-12.85979918185199</v>
+        <v>-19.65394535665472</v>
       </c>
       <c r="H36" t="b">
         <v>0</v>
@@ -2123,7 +2135,7 @@
         </is>
       </c>
       <c r="J36" t="n">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
@@ -2141,25 +2153,25 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>TabDDPM</t>
+          <t>WGAN_GP</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>TabDDPM</t>
+          <t>WGAN-GP</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>10.6833</v>
+        <v>2.2412</v>
       </c>
       <c r="E37" t="n">
-        <v>10.5591</v>
+        <v>2.0781</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.1241999999999983</v>
+        <v>-0.1631</v>
       </c>
       <c r="G37" t="n">
-        <v>-1.162562129679016</v>
+        <v>-7.277351418882742</v>
       </c>
       <c r="H37" t="b">
         <v>0</v>
@@ -2183,30 +2195,30 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Wine</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ForestDiffusion</t>
+          <t>CTABGAN</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Forest Diffusion</t>
+          <t>CTAB-GAN+</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1.6171</v>
+        <v>1.3445</v>
       </c>
       <c r="E38" t="n">
-        <v>1.5167</v>
+        <v>1.1716</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.1004</v>
+        <v>-0.1729000000000001</v>
       </c>
       <c r="G38" t="n">
-        <v>-6.208645105435659</v>
+        <v>-12.85979918185199</v>
       </c>
       <c r="H38" t="b">
         <v>0</v>
@@ -2230,30 +2242,30 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Wine</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>WGAN_GP</t>
+          <t>CTGAN</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>WGAN-GP</t>
+          <t>CTGAN</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>3.6759</v>
+        <v>1.002759</v>
       </c>
       <c r="E39" t="n">
-        <v>3.3891</v>
+        <v>0.721561</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.2867999999999999</v>
+        <v>-0.2811979999999999</v>
       </c>
       <c r="G39" t="n">
-        <v>-7.802170896923201</v>
+        <v>-28.04243093305569</v>
       </c>
       <c r="H39" t="b">
         <v>0</v>
@@ -2264,7 +2276,7 @@
         </is>
       </c>
       <c r="J39" t="n">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
@@ -2277,30 +2289,30 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Wine</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CTABGAN</t>
+          <t>TabDDPM</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CTAB-GAN+</t>
+          <t>TabDDPM</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>3.3377</v>
+        <v>10.6833</v>
       </c>
       <c r="E40" t="n">
-        <v>3.1203</v>
+        <v>10.5591</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.2174</v>
+        <v>-0.1241999999999983</v>
       </c>
       <c r="G40" t="n">
-        <v>-6.513467357761334</v>
+        <v>-1.162562129679016</v>
       </c>
       <c r="H40" t="b">
         <v>0</v>
@@ -2324,30 +2336,30 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Wine</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>TabDDPM</t>
+          <t>CopulaGAN</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>TabDDPM</t>
+          <t>Copula GAN</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>5.4729</v>
+        <v>1.267484</v>
       </c>
       <c r="E41" t="n">
-        <v>5.1842</v>
+        <v>0.973256</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.2887000000000004</v>
+        <v>-0.294228</v>
       </c>
       <c r="G41" t="n">
-        <v>-5.275082680114754</v>
+        <v>-23.21354746884379</v>
       </c>
       <c r="H41" t="b">
         <v>0</v>
@@ -2358,7 +2370,7 @@
         </is>
       </c>
       <c r="J41" t="n">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
@@ -2371,7 +2383,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CDC</t>
+          <t>Wine</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2385,16 +2397,16 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>2.7934</v>
+        <v>1.6171</v>
       </c>
       <c r="E42" t="n">
-        <v>2.6942</v>
+        <v>1.5167</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.09920000000000018</v>
+        <v>-0.1004</v>
       </c>
       <c r="G42" t="n">
-        <v>-3.551227894322337</v>
+        <v>-6.208645105435659</v>
       </c>
       <c r="H42" t="b">
         <v>0</v>
@@ -2418,7 +2430,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CDC</t>
+          <t>Wine</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2432,16 +2444,16 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>3.0372</v>
+        <v>2.550131147570549</v>
       </c>
       <c r="E43" t="n">
-        <v>2.801934</v>
+        <v>2.062422642354435</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.2352659999999998</v>
+        <v>-0.4877085052161139</v>
       </c>
       <c r="G43" t="n">
-        <v>-7.74614776768075</v>
+        <v>-19.12484013540804</v>
       </c>
       <c r="H43" t="b">
         <v>0</v>
@@ -2452,7 +2464,7 @@
         </is>
       </c>
       <c r="J43" t="n">
-        <v>5000</v>
+        <v>6497</v>
       </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
@@ -2465,7 +2477,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CDC</t>
+          <t>Wine</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2479,16 +2491,16 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>3.956109</v>
+        <v>2.167596417725627</v>
       </c>
       <c r="E44" t="n">
-        <v>3.569087</v>
+        <v>2.011109817987401</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.387022</v>
+        <v>-0.1564865997382263</v>
       </c>
       <c r="G44" t="n">
-        <v>-9.782895264008145</v>
+        <v>-7.219360507267377</v>
       </c>
       <c r="H44" t="b">
         <v>0</v>
@@ -2499,7 +2511,7 @@
         </is>
       </c>
       <c r="J44" t="n">
-        <v>5000</v>
+        <v>6497</v>
       </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
@@ -2512,7 +2524,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CDC</t>
+          <t>Wine</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2526,16 +2538,16 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>3.9642</v>
+        <v>3.6759</v>
       </c>
       <c r="E45" t="n">
-        <v>3.8121</v>
+        <v>3.3891</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.1520999999999999</v>
+        <v>-0.2867999999999999</v>
       </c>
       <c r="G45" t="n">
-        <v>-3.836839715453304</v>
+        <v>-7.802170896923201</v>
       </c>
       <c r="H45" t="b">
         <v>0</v>
@@ -2559,7 +2571,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CDC</t>
+          <t>Wine</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2573,16 +2585,16 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>6.856</v>
+        <v>3.3377</v>
       </c>
       <c r="E46" t="n">
-        <v>6.7014</v>
+        <v>3.1203</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.1546000000000003</v>
+        <v>-0.2174</v>
       </c>
       <c r="G46" t="n">
-        <v>-2.254959159859981</v>
+        <v>-6.513467357761334</v>
       </c>
       <c r="H46" t="b">
         <v>0</v>
@@ -2606,7 +2618,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CDC</t>
+          <t>Wine</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2620,16 +2632,16 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>3.446302</v>
+        <v>3.501071108209549</v>
       </c>
       <c r="E47" t="n">
-        <v>3.072402</v>
+        <v>3.096475460767122</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.3739000000000003</v>
+        <v>-0.4045956474424273</v>
       </c>
       <c r="G47" t="n">
-        <v>-10.84931036223756</v>
+        <v>-11.55633904417719</v>
       </c>
       <c r="H47" t="b">
         <v>0</v>
@@ -2640,7 +2652,7 @@
         </is>
       </c>
       <c r="J47" t="n">
-        <v>5000</v>
+        <v>6497</v>
       </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
@@ -2653,7 +2665,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>CDC</t>
+          <t>Wine</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2667,16 +2679,16 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>8.513500000000001</v>
+        <v>5.4729</v>
       </c>
       <c r="E48" t="n">
-        <v>8.3148</v>
+        <v>5.1842</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.1987000000000005</v>
+        <v>-0.2887000000000004</v>
       </c>
       <c r="G48" t="n">
-        <v>-2.333940212603518</v>
+        <v>-5.275082680114754</v>
       </c>
       <c r="H48" t="b">
         <v>0</v>
@@ -2700,7 +2712,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>CDC</t>
+          <t>Wine</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2714,16 +2726,16 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>3.788867</v>
+        <v>3.171785053292916</v>
       </c>
       <c r="E49" t="n">
-        <v>3.345442</v>
+        <v>2.740441860745499</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.4434250000000004</v>
+        <v>-0.4313431925474172</v>
       </c>
       <c r="G49" t="n">
-        <v>-11.70336673206002</v>
+        <v>-13.59938284908685</v>
       </c>
       <c r="H49" t="b">
         <v>0</v>
@@ -2734,7 +2746,7 @@
         </is>
       </c>
       <c r="J49" t="n">
-        <v>5000</v>
+        <v>6497</v>
       </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
@@ -2747,7 +2759,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Mushroom</t>
+          <t>CDC</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2761,16 +2773,16 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>0.6321</v>
+        <v>2.7934</v>
       </c>
       <c r="E50" t="n">
-        <v>0.5276</v>
+        <v>2.6942</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.1045</v>
+        <v>-0.09920000000000018</v>
       </c>
       <c r="G50" t="n">
-        <v>-16.53219427305806</v>
+        <v>-3.551227894322337</v>
       </c>
       <c r="H50" t="b">
         <v>0</v>
@@ -2794,7 +2806,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Mushroom</t>
+          <t>CDC</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2808,16 +2820,16 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0.544045</v>
+        <v>3.0372</v>
       </c>
       <c r="E51" t="n">
-        <v>0.433018</v>
+        <v>2.801934</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.111027</v>
+        <v>-0.2352659999999998</v>
       </c>
       <c r="G51" t="n">
-        <v>-20.40768686413807</v>
+        <v>-7.74614776768075</v>
       </c>
       <c r="H51" t="b">
         <v>0</v>
@@ -2828,7 +2840,7 @@
         </is>
       </c>
       <c r="J51" t="n">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
@@ -2841,7 +2853,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Mushroom</t>
+          <t>CDC</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2855,16 +2867,16 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0.538448</v>
+        <v>3.956109</v>
       </c>
       <c r="E52" t="n">
-        <v>0.394057</v>
+        <v>3.569087</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.144391</v>
+        <v>-0.387022</v>
       </c>
       <c r="G52" t="n">
-        <v>-26.81614566309096</v>
+        <v>-9.782895264008145</v>
       </c>
       <c r="H52" t="b">
         <v>0</v>
@@ -2875,7 +2887,7 @@
         </is>
       </c>
       <c r="J52" t="n">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
@@ -2888,7 +2900,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Mushroom</t>
+          <t>CDC</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2902,16 +2914,16 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1.1701</v>
+        <v>3.9642</v>
       </c>
       <c r="E53" t="n">
-        <v>1.0407</v>
+        <v>3.8121</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.1294</v>
+        <v>-0.1520999999999999</v>
       </c>
       <c r="G53" t="n">
-        <v>-11.05888385608067</v>
+        <v>-3.836839715453304</v>
       </c>
       <c r="H53" t="b">
         <v>0</v>
@@ -2935,7 +2947,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Mushroom</t>
+          <t>CDC</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2949,16 +2961,16 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1.9831</v>
+        <v>6.856</v>
       </c>
       <c r="E54" t="n">
-        <v>1.8176</v>
+        <v>6.7014</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.1655</v>
+        <v>-0.1546000000000003</v>
       </c>
       <c r="G54" t="n">
-        <v>-8.345519640966163</v>
+        <v>-2.254959159859981</v>
       </c>
       <c r="H54" t="b">
         <v>0</v>
@@ -2982,7 +2994,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Mushroom</t>
+          <t>CDC</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2996,16 +3008,16 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.615897</v>
+        <v>3.446302</v>
       </c>
       <c r="E55" t="n">
-        <v>0.486169</v>
+        <v>3.072402</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.129728</v>
+        <v>-0.3739000000000003</v>
       </c>
       <c r="G55" t="n">
-        <v>-21.06326220130964</v>
+        <v>-10.84931036223756</v>
       </c>
       <c r="H55" t="b">
         <v>0</v>
@@ -3016,7 +3028,7 @@
         </is>
       </c>
       <c r="J55" t="n">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
@@ -3029,7 +3041,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Mushroom</t>
+          <t>CDC</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3043,16 +3055,16 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>9.373900000000001</v>
+        <v>8.513500000000001</v>
       </c>
       <c r="E56" t="n">
-        <v>9.2433</v>
+        <v>8.3148</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.1306000000000012</v>
+        <v>-0.1987000000000005</v>
       </c>
       <c r="G56" t="n">
-        <v>-1.393230139002989</v>
+        <v>-2.333940212603518</v>
       </c>
       <c r="H56" t="b">
         <v>0</v>
@@ -3076,7 +3088,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Mushroom</t>
+          <t>CDC</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3090,16 +3102,16 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>0.698264</v>
+        <v>3.788867</v>
       </c>
       <c r="E57" t="n">
-        <v>0.539467</v>
+        <v>3.345442</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.158797</v>
+        <v>-0.4434250000000004</v>
       </c>
       <c r="G57" t="n">
-        <v>-22.74168509331713</v>
+        <v>-11.70336673206002</v>
       </c>
       <c r="H57" t="b">
         <v>0</v>
@@ -3110,7 +3122,7 @@
         </is>
       </c>
       <c r="J57" t="n">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
@@ -3123,7 +3135,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>MAGIC</t>
+          <t>Mushroom</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3137,16 +3149,16 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1.432</v>
+        <v>0.6321</v>
       </c>
       <c r="E58" t="n">
-        <v>1.3078</v>
+        <v>0.5276</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.1241999999999999</v>
+        <v>-0.1045</v>
       </c>
       <c r="G58" t="n">
-        <v>-8.67318435754189</v>
+        <v>-16.53219427305806</v>
       </c>
       <c r="H58" t="b">
         <v>0</v>
@@ -3170,7 +3182,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>MAGIC</t>
+          <t>Mushroom</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3184,27 +3196,27 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1.25837</v>
+        <v>0.544045</v>
       </c>
       <c r="E59" t="n">
-        <v>2.000846</v>
+        <v>0.433018</v>
       </c>
       <c r="F59" t="n">
-        <v>0.7424760000000001</v>
+        <v>-0.111027</v>
       </c>
       <c r="G59" t="n">
-        <v>59.00299593919119</v>
+        <v>-20.40768686413807</v>
       </c>
       <c r="H59" t="b">
         <v>0</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Hungarian worse (higher distance)</t>
+          <t>Hungarian better (lower distance)</t>
         </is>
       </c>
       <c r="J59" t="n">
-        <v>19020</v>
+        <v>10000</v>
       </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
@@ -3217,7 +3229,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>MAGIC</t>
+          <t>Mushroom</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3231,27 +3243,27 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1.948976</v>
+        <v>0.538448</v>
       </c>
       <c r="E60" t="n">
-        <v>2.490962</v>
+        <v>0.394057</v>
       </c>
       <c r="F60" t="n">
-        <v>0.5419860000000001</v>
+        <v>-0.144391</v>
       </c>
       <c r="G60" t="n">
-        <v>27.80875700880873</v>
+        <v>-26.81614566309096</v>
       </c>
       <c r="H60" t="b">
         <v>0</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Hungarian worse (higher distance)</t>
+          <t>Hungarian better (lower distance)</t>
         </is>
       </c>
       <c r="J60" t="n">
-        <v>19020</v>
+        <v>10000</v>
       </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
@@ -3264,7 +3276,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>MAGIC</t>
+          <t>Mushroom</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3278,16 +3290,16 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1.209</v>
+        <v>1.1701</v>
       </c>
       <c r="E61" t="n">
-        <v>1.1898</v>
+        <v>1.0407</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.01920000000000011</v>
+        <v>-0.1294</v>
       </c>
       <c r="G61" t="n">
-        <v>-1.588089330024823</v>
+        <v>-11.05888385608067</v>
       </c>
       <c r="H61" t="b">
         <v>0</v>
@@ -3311,7 +3323,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>MAGIC</t>
+          <t>Mushroom</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3325,16 +3337,16 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1.9498</v>
+        <v>1.9831</v>
       </c>
       <c r="E62" t="n">
-        <v>1.8741</v>
+        <v>1.8176</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.07569999999999988</v>
+        <v>-0.1655</v>
       </c>
       <c r="G62" t="n">
-        <v>-3.882449481998147</v>
+        <v>-8.345519640966163</v>
       </c>
       <c r="H62" t="b">
         <v>0</v>
@@ -3358,7 +3370,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>MAGIC</t>
+          <t>Mushroom</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3372,27 +3384,27 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>2.43384</v>
+        <v>0.615897</v>
       </c>
       <c r="E63" t="n">
-        <v>3.383397</v>
+        <v>0.486169</v>
       </c>
       <c r="F63" t="n">
-        <v>0.949557</v>
+        <v>-0.129728</v>
       </c>
       <c r="G63" t="n">
-        <v>39.01476678828518</v>
+        <v>-21.06326220130964</v>
       </c>
       <c r="H63" t="b">
         <v>0</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Hungarian worse (higher distance)</t>
+          <t>Hungarian better (lower distance)</t>
         </is>
       </c>
       <c r="J63" t="n">
-        <v>19020</v>
+        <v>10000</v>
       </c>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
@@ -3405,7 +3417,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>MAGIC</t>
+          <t>Mushroom</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3419,16 +3431,16 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>4.5721</v>
+        <v>9.373900000000001</v>
       </c>
       <c r="E64" t="n">
-        <v>4.2848</v>
+        <v>9.2433</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.2873000000000001</v>
+        <v>-0.1306000000000012</v>
       </c>
       <c r="G64" t="n">
-        <v>-6.283764572078478</v>
+        <v>-1.393230139002989</v>
       </c>
       <c r="H64" t="b">
         <v>0</v>
@@ -3452,7 +3464,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>MAGIC</t>
+          <t>Mushroom</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3466,16 +3478,16 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1.952442</v>
+        <v>0.698264</v>
       </c>
       <c r="E65" t="n">
-        <v>1.282184</v>
+        <v>0.539467</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.670258</v>
+        <v>-0.158797</v>
       </c>
       <c r="G65" t="n">
-        <v>-34.32921438895496</v>
+        <v>-22.74168509331713</v>
       </c>
       <c r="H65" t="b">
         <v>0</v>
@@ -3486,7 +3498,7 @@
         </is>
       </c>
       <c r="J65" t="n">
-        <v>19020</v>
+        <v>10000</v>
       </c>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
@@ -3499,7 +3511,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Metro</t>
+          <t>MAGIC</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3513,16 +3525,16 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0.35574</v>
+        <v>1.432</v>
       </c>
       <c r="E66" t="n">
-        <v>0.297551</v>
+        <v>1.3078</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.05818899999999999</v>
+        <v>-0.1241999999999999</v>
       </c>
       <c r="G66" t="n">
-        <v>-16.35717096756058</v>
+        <v>-8.67318435754189</v>
       </c>
       <c r="H66" t="b">
         <v>0</v>
@@ -3546,7 +3558,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Metro</t>
+          <t>MAGIC</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3560,16 +3572,16 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>0.258434</v>
+        <v>1.25837</v>
       </c>
       <c r="E67" t="n">
-        <v>0.291262</v>
+        <v>2.000846</v>
       </c>
       <c r="F67" t="n">
-        <v>0.03282800000000002</v>
+        <v>0.7424760000000001</v>
       </c>
       <c r="G67" t="n">
-        <v>12.70266296230373</v>
+        <v>59.00299593919119</v>
       </c>
       <c r="H67" t="b">
         <v>0</v>
@@ -3580,7 +3592,7 @@
         </is>
       </c>
       <c r="J67" t="n">
-        <v>5000</v>
+        <v>19020</v>
       </c>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
@@ -3593,7 +3605,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Metro</t>
+          <t>MAGIC</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3607,27 +3619,27 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>27.853218</v>
+        <v>1.948976</v>
       </c>
       <c r="E68" t="n">
-        <v>27.790041</v>
+        <v>2.490962</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.06317699999999959</v>
+        <v>0.5419860000000001</v>
       </c>
       <c r="G68" t="n">
-        <v>-0.2268211881298585</v>
+        <v>27.80875700880873</v>
       </c>
       <c r="H68" t="b">
         <v>0</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Hungarian better (lower distance)</t>
+          <t>Hungarian worse (higher distance)</t>
         </is>
       </c>
       <c r="J68" t="n">
-        <v>5000</v>
+        <v>19020</v>
       </c>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
@@ -3640,7 +3652,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Metro</t>
+          <t>MAGIC</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3654,16 +3666,16 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1.498572</v>
+        <v>1.209</v>
       </c>
       <c r="E69" t="n">
-        <v>1.410562</v>
+        <v>1.1898</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.08800999999999992</v>
+        <v>-0.01920000000000011</v>
       </c>
       <c r="G69" t="n">
-        <v>-5.872924357321497</v>
+        <v>-1.588089330024823</v>
       </c>
       <c r="H69" t="b">
         <v>0</v>
@@ -3687,7 +3699,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Metro</t>
+          <t>MAGIC</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3701,16 +3713,16 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1.607389</v>
+        <v>1.9498</v>
       </c>
       <c r="E70" t="n">
-        <v>1.468671</v>
+        <v>1.8741</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.1387179999999999</v>
+        <v>-0.07569999999999988</v>
       </c>
       <c r="G70" t="n">
-        <v>-8.630020486640129</v>
+        <v>-3.882449481998147</v>
       </c>
       <c r="H70" t="b">
         <v>0</v>
@@ -3734,7 +3746,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Metro</t>
+          <t>MAGIC</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3748,27 +3760,27 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>0.431625</v>
+        <v>2.43384</v>
       </c>
       <c r="E71" t="n">
-        <v>0.399805</v>
+        <v>3.383397</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.03181999999999996</v>
+        <v>0.949557</v>
       </c>
       <c r="G71" t="n">
-        <v>-7.372140167969873</v>
+        <v>39.01476678828518</v>
       </c>
       <c r="H71" t="b">
         <v>0</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Hungarian better (lower distance)</t>
+          <t>Hungarian worse (higher distance)</t>
         </is>
       </c>
       <c r="J71" t="n">
-        <v>5000</v>
+        <v>19020</v>
       </c>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
@@ -3781,7 +3793,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Metro</t>
+          <t>MAGIC</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3795,16 +3807,16 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>13.596022</v>
+        <v>4.5721</v>
       </c>
       <c r="E72" t="n">
-        <v>13.548747</v>
+        <v>4.2848</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.04727499999999907</v>
+        <v>-0.2873000000000001</v>
       </c>
       <c r="G72" t="n">
-        <v>-0.3477119998776044</v>
+        <v>-6.283764572078478</v>
       </c>
       <c r="H72" t="b">
         <v>0</v>
@@ -3828,7 +3840,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Metro</t>
+          <t>MAGIC</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3842,27 +3854,27 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>0.587039</v>
+        <v>2.200845</v>
       </c>
       <c r="E73" t="n">
-        <v>0.482782</v>
+        <v>3.055436</v>
       </c>
       <c r="F73" t="n">
-        <v>-0.104257</v>
+        <v>0.8545909999999997</v>
       </c>
       <c r="G73" t="n">
-        <v>-17.75980812177726</v>
+        <v>38.83013115417031</v>
       </c>
       <c r="H73" t="b">
         <v>0</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Hungarian better (lower distance)</t>
+          <t>Hungarian worse (higher distance)</t>
         </is>
       </c>
       <c r="J73" t="n">
-        <v>5000</v>
+        <v>19020</v>
       </c>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
@@ -3875,7 +3887,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>OnlineShop</t>
+          <t>Metro</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3889,16 +3901,16 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1.94589</v>
+        <v>0.35574</v>
       </c>
       <c r="E74" t="n">
-        <v>1.816702</v>
+        <v>0.297551</v>
       </c>
       <c r="F74" t="n">
-        <v>-0.1291879999999999</v>
+        <v>-0.05818899999999999</v>
       </c>
       <c r="G74" t="n">
-        <v>-6.639018649563947</v>
+        <v>-16.35717096756058</v>
       </c>
       <c r="H74" t="b">
         <v>0</v>
@@ -3922,41 +3934,41 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>OnlineShop</t>
+          <t>Metro</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>WGAN_GP</t>
+          <t>TVAE</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>WGAN-GP</t>
+          <t>TVAE</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>3.20519</v>
+        <v>0.258434</v>
       </c>
       <c r="E75" t="n">
-        <v>3.055943</v>
+        <v>0.291262</v>
       </c>
       <c r="F75" t="n">
-        <v>-0.1492469999999999</v>
+        <v>0.03282800000000002</v>
       </c>
       <c r="G75" t="n">
-        <v>-4.65641662428748</v>
+        <v>12.70266296230373</v>
       </c>
       <c r="H75" t="b">
         <v>0</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Hungarian better (lower distance)</t>
+          <t>Hungarian worse (higher distance)</t>
         </is>
       </c>
       <c r="J75" t="n">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
@@ -3969,30 +3981,30 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>OnlineShop</t>
+          <t>Metro</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>CTABGAN</t>
+          <t>GaussianCopula</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>CTAB-GAN+</t>
+          <t>Gaussian Copula</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>2.588096</v>
+        <v>27.853218</v>
       </c>
       <c r="E76" t="n">
-        <v>2.433242</v>
+        <v>27.790041</v>
       </c>
       <c r="F76" t="n">
-        <v>-0.1548540000000003</v>
+        <v>-0.06317699999999959</v>
       </c>
       <c r="G76" t="n">
-        <v>-5.983317465812716</v>
+        <v>-0.2268211881298585</v>
       </c>
       <c r="H76" t="b">
         <v>0</v>
@@ -4003,7 +4015,7 @@
         </is>
       </c>
       <c r="J76" t="n">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
@@ -4016,30 +4028,30 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>OnlineShop</t>
+          <t>Metro</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>TabDDPM</t>
+          <t>WGAN_GP</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>TabDDPM</t>
+          <t>WGAN-GP</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>5.801993</v>
+        <v>1.498572</v>
       </c>
       <c r="E77" t="n">
-        <v>5.638238</v>
+        <v>1.410562</v>
       </c>
       <c r="F77" t="n">
-        <v>-0.1637550000000001</v>
+        <v>-0.08800999999999992</v>
       </c>
       <c r="G77" t="n">
-        <v>-2.822392236598701</v>
+        <v>-5.872924357321497</v>
       </c>
       <c r="H77" t="b">
         <v>0</v>
@@ -4063,30 +4075,30 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>AirQuality</t>
+          <t>Metro</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ForestDiffusion</t>
+          <t>CTABGAN</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Forest Diffusion</t>
+          <t>CTAB-GAN+</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1.7287</v>
+        <v>1.607389</v>
       </c>
       <c r="E78" t="n">
-        <v>1.6389</v>
+        <v>1.468671</v>
       </c>
       <c r="F78" t="n">
-        <v>-0.08979999999999988</v>
+        <v>-0.1387179999999999</v>
       </c>
       <c r="G78" t="n">
-        <v>-5.19465494302076</v>
+        <v>-8.630020486640129</v>
       </c>
       <c r="H78" t="b">
         <v>0</v>
@@ -4110,30 +4122,30 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>AirQuality</t>
+          <t>Metro</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>TVAE</t>
+          <t>CTGAN</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>TVAE</t>
+          <t>CTGAN</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>53.42266</v>
+        <v>0.431625</v>
       </c>
       <c r="E79" t="n">
-        <v>20.605003</v>
+        <v>0.399805</v>
       </c>
       <c r="F79" t="n">
-        <v>-32.817657</v>
+        <v>-0.03181999999999996</v>
       </c>
       <c r="G79" t="n">
-        <v>-61.43021893705779</v>
+        <v>-7.372140167969873</v>
       </c>
       <c r="H79" t="b">
         <v>0</v>
@@ -4144,7 +4156,7 @@
         </is>
       </c>
       <c r="J79" t="n">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
@@ -4157,30 +4169,30 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>AirQuality</t>
+          <t>Metro</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>GaussianCopula</t>
+          <t>TabDDPM</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Gaussian Copula</t>
+          <t>TabDDPM</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>28.73888</v>
+        <v>13.596022</v>
       </c>
       <c r="E80" t="n">
-        <v>18.531944</v>
+        <v>13.548747</v>
       </c>
       <c r="F80" t="n">
-        <v>-10.206936</v>
+        <v>-0.04727499999999907</v>
       </c>
       <c r="G80" t="n">
-        <v>-35.51612310570211</v>
+        <v>-0.3477119998776044</v>
       </c>
       <c r="H80" t="b">
         <v>0</v>
@@ -4204,30 +4216,30 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>AirQuality</t>
+          <t>Metro</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>WGAN_GP</t>
+          <t>CopulaGAN</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>WGAN-GP</t>
+          <t>Copula GAN</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>4.9184</v>
+        <v>0.587039</v>
       </c>
       <c r="E81" t="n">
-        <v>4.6189</v>
+        <v>0.482782</v>
       </c>
       <c r="F81" t="n">
-        <v>-0.2995000000000001</v>
+        <v>-0.104257</v>
       </c>
       <c r="G81" t="n">
-        <v>-6.089378659726743</v>
+        <v>-17.75980812177726</v>
       </c>
       <c r="H81" t="b">
         <v>0</v>
@@ -4237,7 +4249,9 @@
           <t>Hungarian better (lower distance)</t>
         </is>
       </c>
-      <c r="J81" t="inlineStr"/>
+      <c r="J81" t="n">
+        <v>5000</v>
+      </c>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
@@ -4249,30 +4263,30 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>AirQuality</t>
+          <t>OnlineShop</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>CTABGAN</t>
+          <t>ForestDiffusion</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>CTAB-GAN+</t>
+          <t>Forest Diffusion</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>9.283799999999999</v>
+        <v>1.94589</v>
       </c>
       <c r="E82" t="n">
-        <v>9.02</v>
+        <v>1.816702</v>
       </c>
       <c r="F82" t="n">
-        <v>-0.2637999999999998</v>
+        <v>-0.1291879999999999</v>
       </c>
       <c r="G82" t="n">
-        <v>-2.841508864904455</v>
+        <v>-6.639018649563947</v>
       </c>
       <c r="H82" t="b">
         <v>0</v>
@@ -4282,7 +4296,9 @@
           <t>Hungarian better (lower distance)</t>
         </is>
       </c>
-      <c r="J82" t="inlineStr"/>
+      <c r="J82" t="n">
+        <v>1000</v>
+      </c>
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
@@ -4294,30 +4310,30 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>AirQuality</t>
+          <t>OnlineShop</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>TabDDPM</t>
+          <t>TVAE</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>TabDDPM</t>
+          <t>TVAE</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>6.392</v>
+        <v>2.525588</v>
       </c>
       <c r="E83" t="n">
-        <v>6.1055</v>
+        <v>2.384212</v>
       </c>
       <c r="F83" t="n">
-        <v>-0.2865000000000002</v>
+        <v>-0.1413759999999997</v>
       </c>
       <c r="G83" t="n">
-        <v>-4.482165206508138</v>
+        <v>-5.597745950645938</v>
       </c>
       <c r="H83" t="b">
         <v>0</v>
@@ -4327,9 +4343,7 @@
           <t>Hungarian better (lower distance)</t>
         </is>
       </c>
-      <c r="J83" t="n">
-        <v>1000</v>
-      </c>
+      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
@@ -4341,30 +4355,30 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Concrete</t>
+          <t>OnlineShop</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>ForestDiffusion</t>
+          <t>GaussianCopula</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Forest Diffusion</t>
+          <t>Gaussian Copula</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>0.9112</v>
+        <v>1.722005</v>
       </c>
       <c r="E84" t="n">
-        <v>0.8489</v>
+        <v>1.587593</v>
       </c>
       <c r="F84" t="n">
-        <v>-0.06230000000000002</v>
+        <v>-0.134412</v>
       </c>
       <c r="G84" t="n">
-        <v>-6.837137840210714</v>
+        <v>-7.805552248686849</v>
       </c>
       <c r="H84" t="b">
         <v>0</v>
@@ -4374,9 +4388,7 @@
           <t>Hungarian better (lower distance)</t>
         </is>
       </c>
-      <c r="J84" t="n">
-        <v>1000</v>
-      </c>
+      <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
@@ -4388,30 +4400,30 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Concrete</t>
+          <t>OnlineShop</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>TVAE</t>
+          <t>WGAN_GP</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>TVAE</t>
+          <t>WGAN-GP</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>3.345275</v>
+        <v>3.20519</v>
       </c>
       <c r="E85" t="n">
-        <v>3.145877</v>
+        <v>3.055943</v>
       </c>
       <c r="F85" t="n">
-        <v>-0.199398</v>
+        <v>-0.1492469999999999</v>
       </c>
       <c r="G85" t="n">
-        <v>-5.960586199938719</v>
+        <v>-4.65641662428748</v>
       </c>
       <c r="H85" t="b">
         <v>0</v>
@@ -4435,30 +4447,30 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Concrete</t>
+          <t>OnlineShop</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>GaussianCopula</t>
+          <t>CTABGAN</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Gaussian Copula</t>
+          <t>CTAB-GAN+</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>3.985879</v>
+        <v>2.588096</v>
       </c>
       <c r="E86" t="n">
-        <v>3.685769</v>
+        <v>2.433242</v>
       </c>
       <c r="F86" t="n">
-        <v>-0.3001100000000001</v>
+        <v>-0.1548540000000003</v>
       </c>
       <c r="G86" t="n">
-        <v>-7.529330418710655</v>
+        <v>-5.983317465812716</v>
       </c>
       <c r="H86" t="b">
         <v>0</v>
@@ -4482,30 +4494,30 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Concrete</t>
+          <t>OnlineShop</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>WGAN_GP</t>
+          <t>CTGAN</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>WGAN-GP</t>
+          <t>CTGAN</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>3.6759</v>
+        <v>1.712434</v>
       </c>
       <c r="E87" t="n">
-        <v>3.3891</v>
+        <v>1.567794</v>
       </c>
       <c r="F87" t="n">
-        <v>-0.2867999999999999</v>
+        <v>-0.1446400000000001</v>
       </c>
       <c r="G87" t="n">
-        <v>-7.802170896923201</v>
+        <v>-8.446456914543866</v>
       </c>
       <c r="H87" t="b">
         <v>0</v>
@@ -4515,9 +4527,7 @@
           <t>Hungarian better (lower distance)</t>
         </is>
       </c>
-      <c r="J87" t="n">
-        <v>1000</v>
-      </c>
+      <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr">
@@ -4529,30 +4539,30 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Concrete</t>
+          <t>OnlineShop</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>CTABGAN</t>
+          <t>TabDDPM</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>CTAB-GAN+</t>
+          <t>TabDDPM</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>3.3377</v>
+        <v>5.801993</v>
       </c>
       <c r="E88" t="n">
-        <v>3.1203</v>
+        <v>5.638238</v>
       </c>
       <c r="F88" t="n">
-        <v>-0.2174</v>
+        <v>-0.1637550000000001</v>
       </c>
       <c r="G88" t="n">
-        <v>-6.513467357761334</v>
+        <v>-2.822392236598701</v>
       </c>
       <c r="H88" t="b">
         <v>0</v>
@@ -4576,30 +4586,30 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Concrete</t>
+          <t>OnlineShop</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>CTGAN</t>
+          <t>CopulaGAN</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>CTGAN</t>
+          <t>Copula GAN</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>5.242352</v>
+        <v>1.741369</v>
       </c>
       <c r="E89" t="n">
-        <v>5.018745</v>
+        <v>1.581511</v>
       </c>
       <c r="F89" t="n">
-        <v>-0.2236070000000003</v>
+        <v>-0.1598580000000001</v>
       </c>
       <c r="G89" t="n">
-        <v>-4.265394616767442</v>
+        <v>-9.180018709417709</v>
       </c>
       <c r="H89" t="b">
         <v>0</v>
@@ -4609,9 +4619,7 @@
           <t>Hungarian better (lower distance)</t>
         </is>
       </c>
-      <c r="J89" t="n">
-        <v>1000</v>
-      </c>
+      <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
@@ -4623,30 +4631,30 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Concrete</t>
+          <t>AirQuality</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>TabDDPM</t>
+          <t>ForestDiffusion</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>TabDDPM</t>
+          <t>Forest Diffusion</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1.7551</v>
+        <v>1.7287</v>
       </c>
       <c r="E90" t="n">
-        <v>1.6227</v>
+        <v>1.6389</v>
       </c>
       <c r="F90" t="n">
-        <v>-0.1324000000000001</v>
+        <v>-0.08979999999999988</v>
       </c>
       <c r="G90" t="n">
-        <v>-7.543729702011285</v>
+        <v>-5.19465494302076</v>
       </c>
       <c r="H90" t="b">
         <v>0</v>
@@ -4670,30 +4678,30 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Concrete</t>
+          <t>AirQuality</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>CopulaGAN</t>
+          <t>TVAE</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Copula GAN</t>
+          <t>TVAE</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>6.754965</v>
+        <v>53.42266</v>
       </c>
       <c r="E91" t="n">
-        <v>6.507187</v>
+        <v>20.605003</v>
       </c>
       <c r="F91" t="n">
-        <v>-0.2477780000000003</v>
+        <v>-32.817657</v>
       </c>
       <c r="G91" t="n">
-        <v>-3.668087103338067</v>
+        <v>-61.43021893705779</v>
       </c>
       <c r="H91" t="b">
         <v>0</v>
@@ -4717,30 +4725,30 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>AirQuality</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>ForestDiffusion</t>
+          <t>GaussianCopula</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Forest Diffusion</t>
+          <t>Gaussian Copula</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>41.2109</v>
+        <v>28.73888</v>
       </c>
       <c r="E92" t="n">
-        <v>41.2089</v>
+        <v>18.531944</v>
       </c>
       <c r="F92" t="n">
-        <v>-0.002000000000002444</v>
+        <v>-10.206936</v>
       </c>
       <c r="G92" t="n">
-        <v>-0.004853084984803642</v>
+        <v>-35.51612310570211</v>
       </c>
       <c r="H92" t="b">
         <v>0</v>
@@ -4751,7 +4759,7 @@
         </is>
       </c>
       <c r="J92" t="n">
-        <v>768</v>
+        <v>1000</v>
       </c>
       <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr"/>
@@ -4764,30 +4772,30 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>AirQuality</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>TVAE</t>
+          <t>WGAN_GP</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>TVAE</t>
+          <t>WGAN-GP</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>18868.031041</v>
+        <v>4.9184</v>
       </c>
       <c r="E93" t="n">
-        <v>18868.030988</v>
+        <v>4.6189</v>
       </c>
       <c r="F93" t="n">
-        <v>-5.299999975250103e-05</v>
+        <v>-0.2995000000000001</v>
       </c>
       <c r="G93" t="n">
-        <v>-2.808984129681188e-07</v>
+        <v>-6.089378659726743</v>
       </c>
       <c r="H93" t="b">
         <v>0</v>
@@ -4797,9 +4805,7 @@
           <t>Hungarian better (lower distance)</t>
         </is>
       </c>
-      <c r="J93" t="n">
-        <v>768</v>
-      </c>
+      <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
@@ -4811,30 +4817,30 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>AirQuality</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>GaussianCopula</t>
+          <t>CTABGAN</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Gaussian Copula</t>
+          <t>CTAB-GAN+</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>21169.768599</v>
+        <v>9.283799999999999</v>
       </c>
       <c r="E94" t="n">
-        <v>21169.768524</v>
+        <v>9.02</v>
       </c>
       <c r="F94" t="n">
-        <v>-7.499999992433004e-05</v>
+        <v>-0.2637999999999998</v>
       </c>
       <c r="G94" t="n">
-        <v>-3.542787894614627e-07</v>
+        <v>-2.841508864904455</v>
       </c>
       <c r="H94" t="b">
         <v>0</v>
@@ -4844,9 +4850,7 @@
           <t>Hungarian better (lower distance)</t>
         </is>
       </c>
-      <c r="J94" t="n">
-        <v>768</v>
-      </c>
+      <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
@@ -4858,41 +4862,41 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>AirQuality</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>WGAN_GP</t>
+          <t>CTGAN</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>WGAN-GP</t>
+          <t>CTGAN</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>23616.3467</v>
+        <v>15.87754573663957</v>
       </c>
       <c r="E95" t="n">
-        <v>23616.3467</v>
+        <v>15.58214745304394</v>
       </c>
       <c r="F95" t="n">
-        <v>0</v>
+        <v>-0.2953982835956328</v>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>-1.860478240752043</v>
       </c>
       <c r="H95" t="b">
         <v>0</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Negligible / tie</t>
+          <t>Hungarian better (lower distance)</t>
         </is>
       </c>
       <c r="J95" t="n">
-        <v>768</v>
+        <v>1000</v>
       </c>
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr"/>
@@ -4905,41 +4909,41 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>AirQuality</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>CTABGAN</t>
+          <t>TabDDPM</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>CTAB-GAN+</t>
+          <t>TabDDPM</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>21021.1892</v>
+        <v>6.392</v>
       </c>
       <c r="E96" t="n">
-        <v>21021.1892</v>
+        <v>6.1055</v>
       </c>
       <c r="F96" t="n">
-        <v>0</v>
+        <v>-0.2865000000000002</v>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>-4.482165206508138</v>
       </c>
       <c r="H96" t="b">
         <v>0</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Negligible / tie</t>
+          <t>Hungarian better (lower distance)</t>
         </is>
       </c>
       <c r="J96" t="n">
-        <v>768</v>
+        <v>1000</v>
       </c>
       <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr"/>
@@ -4952,30 +4956,30 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>AirQuality</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>CTGAN</t>
+          <t>CopulaGAN</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>CTGAN</t>
+          <t>Copula GAN</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>45637.724946</v>
+        <v>17.04914586325495</v>
       </c>
       <c r="E97" t="n">
-        <v>45637.724902</v>
+        <v>16.7797488635705</v>
       </c>
       <c r="F97" t="n">
-        <v>-4.400000034365803e-05</v>
+        <v>-0.2693969996844494</v>
       </c>
       <c r="G97" t="n">
-        <v>-9.641146747722464e-08</v>
+        <v>-1.580120211564765</v>
       </c>
       <c r="H97" t="b">
         <v>0</v>
@@ -4986,7 +4990,7 @@
         </is>
       </c>
       <c r="J97" t="n">
-        <v>768</v>
+        <v>1000</v>
       </c>
       <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr"/>
@@ -4999,41 +5003,41 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Concrete</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>TabDDPM</t>
+          <t>ForestDiffusion</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>TabDDPM</t>
+          <t>Forest Diffusion</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>15946.4815</v>
+        <v>0.9112</v>
       </c>
       <c r="E98" t="n">
-        <v>15946.4815</v>
+        <v>0.8489</v>
       </c>
       <c r="F98" t="n">
-        <v>0</v>
+        <v>-0.06230000000000002</v>
       </c>
       <c r="G98" t="n">
-        <v>0</v>
+        <v>-6.837137840210714</v>
       </c>
       <c r="H98" t="b">
         <v>0</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Negligible / tie</t>
+          <t>Hungarian better (lower distance)</t>
         </is>
       </c>
       <c r="J98" t="n">
-        <v>768</v>
+        <v>1000</v>
       </c>
       <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr"/>
@@ -5046,30 +5050,30 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Concrete</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>CopulaGAN</t>
+          <t>TVAE</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Copula GAN</t>
+          <t>TVAE</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>51117.382605</v>
+        <v>3.345275</v>
       </c>
       <c r="E99" t="n">
-        <v>51117.382555</v>
+        <v>3.145877</v>
       </c>
       <c r="F99" t="n">
-        <v>-5.000000237487257e-05</v>
+        <v>-0.199398</v>
       </c>
       <c r="G99" t="n">
-        <v>-9.781408950696522e-08</v>
+        <v>-5.960586199938719</v>
       </c>
       <c r="H99" t="b">
         <v>0</v>
@@ -5080,7 +5084,7 @@
         </is>
       </c>
       <c r="J99" t="n">
-        <v>768</v>
+        <v>1000</v>
       </c>
       <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr"/>
@@ -5093,30 +5097,30 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>RealEstate</t>
+          <t>Concrete</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>ForestDiffusion</t>
+          <t>GaussianCopula</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Forest Diffusion</t>
+          <t>Gaussian Copula</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>0.07729999999999999</v>
+        <v>3.985879</v>
       </c>
       <c r="E100" t="n">
-        <v>0.0771</v>
+        <v>3.685769</v>
       </c>
       <c r="F100" t="n">
-        <v>-0.0001999999999999919</v>
+        <v>-0.3001100000000001</v>
       </c>
       <c r="G100" t="n">
-        <v>-0.2587322121604034</v>
+        <v>-7.529330418710655</v>
       </c>
       <c r="H100" t="b">
         <v>0</v>
@@ -5127,7 +5131,7 @@
         </is>
       </c>
       <c r="J100" t="n">
-        <v>414</v>
+        <v>1000</v>
       </c>
       <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr"/>
@@ -5140,30 +5144,30 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>RealEstate</t>
+          <t>Concrete</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>TVAE</t>
+          <t>WGAN_GP</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>TVAE</t>
+          <t>WGAN-GP</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>16693.918272</v>
+        <v>3.6759</v>
       </c>
       <c r="E101" t="n">
-        <v>16693.789109</v>
+        <v>3.3891</v>
       </c>
       <c r="F101" t="n">
-        <v>-0.1291629999977886</v>
+        <v>-0.2867999999999999</v>
       </c>
       <c r="G101" t="n">
-        <v>-0.0007737129048632531</v>
+        <v>-7.802170896923201</v>
       </c>
       <c r="H101" t="b">
         <v>0</v>
@@ -5174,7 +5178,7 @@
         </is>
       </c>
       <c r="J101" t="n">
-        <v>414</v>
+        <v>1000</v>
       </c>
       <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr"/>
@@ -5187,30 +5191,30 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>RealEstate</t>
+          <t>Concrete</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>GaussianCopula</t>
+          <t>CTABGAN</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Gaussian Copula</t>
+          <t>CTAB-GAN+</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>16693.682733</v>
+        <v>3.3377</v>
       </c>
       <c r="E102" t="n">
-        <v>16693.553751</v>
+        <v>3.1203</v>
       </c>
       <c r="F102" t="n">
-        <v>-0.1289820000019972</v>
+        <v>-0.2174</v>
       </c>
       <c r="G102" t="n">
-        <v>-0.0007726395790847645</v>
+        <v>-6.513467357761334</v>
       </c>
       <c r="H102" t="b">
         <v>0</v>
@@ -5221,7 +5225,7 @@
         </is>
       </c>
       <c r="J102" t="n">
-        <v>414</v>
+        <v>1000</v>
       </c>
       <c r="K102" t="inlineStr"/>
       <c r="L102" t="inlineStr"/>
@@ -5234,30 +5238,30 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>RealEstate</t>
+          <t>Concrete</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>WGAN_GP</t>
+          <t>CTGAN</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>WGAN-GP</t>
+          <t>CTGAN</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>1.4639</v>
+        <v>5.242352</v>
       </c>
       <c r="E103" t="n">
-        <v>1.3965</v>
+        <v>5.018745</v>
       </c>
       <c r="F103" t="n">
-        <v>-0.0673999999999999</v>
+        <v>-0.2236070000000003</v>
       </c>
       <c r="G103" t="n">
-        <v>-4.604139627023697</v>
+        <v>-4.265394616767442</v>
       </c>
       <c r="H103" t="b">
         <v>0</v>
@@ -5268,7 +5272,7 @@
         </is>
       </c>
       <c r="J103" t="n">
-        <v>414</v>
+        <v>1000</v>
       </c>
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr"/>
@@ -5281,30 +5285,30 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>RealEstate</t>
+          <t>Concrete</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>CTABGAN</t>
+          <t>TabDDPM</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>CTAB-GAN+</t>
+          <t>TabDDPM</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>0.9013</v>
+        <v>1.7551</v>
       </c>
       <c r="E104" t="n">
-        <v>0.8723</v>
+        <v>1.6227</v>
       </c>
       <c r="F104" t="n">
-        <v>-0.02900000000000003</v>
+        <v>-0.1324000000000001</v>
       </c>
       <c r="G104" t="n">
-        <v>-3.217574614445804</v>
+        <v>-7.543729702011285</v>
       </c>
       <c r="H104" t="b">
         <v>0</v>
@@ -5315,7 +5319,7 @@
         </is>
       </c>
       <c r="J104" t="n">
-        <v>414</v>
+        <v>1000</v>
       </c>
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr"/>
@@ -5328,30 +5332,30 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>RealEstate</t>
+          <t>Concrete</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>CTGAN</t>
+          <t>CopulaGAN</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>CTGAN</t>
+          <t>Copula GAN</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>16692.881415</v>
+        <v>6.754965</v>
       </c>
       <c r="E105" t="n">
-        <v>16692.752234</v>
+        <v>6.507187</v>
       </c>
       <c r="F105" t="n">
-        <v>-0.1291810000002442</v>
+        <v>-0.2477780000000003</v>
       </c>
       <c r="G105" t="n">
-        <v>-0.0007738687934616484</v>
+        <v>-3.668087103338067</v>
       </c>
       <c r="H105" t="b">
         <v>0</v>
@@ -5362,7 +5366,7 @@
         </is>
       </c>
       <c r="J105" t="n">
-        <v>414</v>
+        <v>1000</v>
       </c>
       <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr"/>
@@ -5375,30 +5379,30 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>RealEstate</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>TabDDPM</t>
+          <t>ForestDiffusion</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>TabDDPM</t>
+          <t>Forest Diffusion</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>0.9375</v>
+        <v>41.2109</v>
       </c>
       <c r="E106" t="n">
-        <v>0.8743</v>
+        <v>41.2089</v>
       </c>
       <c r="F106" t="n">
-        <v>-0.06320000000000003</v>
+        <v>-0.002000000000002444</v>
       </c>
       <c r="G106" t="n">
-        <v>-6.741333333333338</v>
+        <v>-0.004853084984803642</v>
       </c>
       <c r="H106" t="b">
         <v>0</v>
@@ -5409,7 +5413,7 @@
         </is>
       </c>
       <c r="J106" t="n">
-        <v>414</v>
+        <v>768</v>
       </c>
       <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr"/>
@@ -5422,30 +5426,30 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>RealEstate</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>CopulaGAN</t>
+          <t>TVAE</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Copula GAN</t>
+          <t>TVAE</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>16693.963602</v>
+        <v>18868.031041</v>
       </c>
       <c r="E107" t="n">
-        <v>16693.834433</v>
+        <v>18868.030988</v>
       </c>
       <c r="F107" t="n">
-        <v>-0.1291689999998198</v>
+        <v>-5.299999975250103e-05</v>
       </c>
       <c r="G107" t="n">
-        <v>-0.000773746745106985</v>
+        <v>-2.808984129681188e-07</v>
       </c>
       <c r="H107" t="b">
         <v>0</v>
@@ -5456,11 +5460,669 @@
         </is>
       </c>
       <c r="J107" t="n">
-        <v>414</v>
+        <v>768</v>
       </c>
       <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr"/>
       <c r="M107" t="inlineStr">
+        <is>
+          <t>Not available in extracted results</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>GaussianCopula</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Gaussian Copula</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>21169.768599</v>
+      </c>
+      <c r="E108" t="n">
+        <v>21169.768524</v>
+      </c>
+      <c r="F108" t="n">
+        <v>-7.499999992433004e-05</v>
+      </c>
+      <c r="G108" t="n">
+        <v>-3.542787894614627e-07</v>
+      </c>
+      <c r="H108" t="b">
+        <v>0</v>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Hungarian better (lower distance)</t>
+        </is>
+      </c>
+      <c r="J108" t="n">
+        <v>768</v>
+      </c>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>Not available in extracted results</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>WGAN_GP</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>WGAN-GP</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>23616.3467</v>
+      </c>
+      <c r="E109" t="n">
+        <v>23616.3467</v>
+      </c>
+      <c r="F109" t="n">
+        <v>0</v>
+      </c>
+      <c r="G109" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" t="b">
+        <v>0</v>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Negligible / tie</t>
+        </is>
+      </c>
+      <c r="J109" t="n">
+        <v>768</v>
+      </c>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>Not available in extracted results</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>CTABGAN</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>CTAB-GAN+</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>21021.1892</v>
+      </c>
+      <c r="E110" t="n">
+        <v>21021.1892</v>
+      </c>
+      <c r="F110" t="n">
+        <v>0</v>
+      </c>
+      <c r="G110" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" t="b">
+        <v>0</v>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Negligible / tie</t>
+        </is>
+      </c>
+      <c r="J110" t="n">
+        <v>768</v>
+      </c>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>Not available in extracted results</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>CTGAN</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>CTGAN</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>45637.724946</v>
+      </c>
+      <c r="E111" t="n">
+        <v>45637.724902</v>
+      </c>
+      <c r="F111" t="n">
+        <v>-4.400000034365803e-05</v>
+      </c>
+      <c r="G111" t="n">
+        <v>-9.641146747722464e-08</v>
+      </c>
+      <c r="H111" t="b">
+        <v>0</v>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Hungarian better (lower distance)</t>
+        </is>
+      </c>
+      <c r="J111" t="n">
+        <v>768</v>
+      </c>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>Not available in extracted results</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>15946.4815</v>
+      </c>
+      <c r="E112" t="n">
+        <v>15946.4815</v>
+      </c>
+      <c r="F112" t="n">
+        <v>0</v>
+      </c>
+      <c r="G112" t="n">
+        <v>0</v>
+      </c>
+      <c r="H112" t="b">
+        <v>0</v>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Negligible / tie</t>
+        </is>
+      </c>
+      <c r="J112" t="n">
+        <v>768</v>
+      </c>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>Not available in extracted results</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>CopulaGAN</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Copula GAN</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>51117.382605</v>
+      </c>
+      <c r="E113" t="n">
+        <v>51117.382555</v>
+      </c>
+      <c r="F113" t="n">
+        <v>-5.000000237487257e-05</v>
+      </c>
+      <c r="G113" t="n">
+        <v>-9.781408950696522e-08</v>
+      </c>
+      <c r="H113" t="b">
+        <v>0</v>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Hungarian better (lower distance)</t>
+        </is>
+      </c>
+      <c r="J113" t="n">
+        <v>768</v>
+      </c>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>Not available in extracted results</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>RealEstate</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Forest Diffusion</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>0.07729999999999999</v>
+      </c>
+      <c r="E114" t="n">
+        <v>0.0771</v>
+      </c>
+      <c r="F114" t="n">
+        <v>-0.0001999999999999919</v>
+      </c>
+      <c r="G114" t="n">
+        <v>-0.2587322121604034</v>
+      </c>
+      <c r="H114" t="b">
+        <v>0</v>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Hungarian better (lower distance)</t>
+        </is>
+      </c>
+      <c r="J114" t="n">
+        <v>414</v>
+      </c>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>Not available in extracted results</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>RealEstate</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>TVAE</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>TVAE</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>16693.918272</v>
+      </c>
+      <c r="E115" t="n">
+        <v>16693.789109</v>
+      </c>
+      <c r="F115" t="n">
+        <v>-0.1291629999977886</v>
+      </c>
+      <c r="G115" t="n">
+        <v>-0.0007737129048632531</v>
+      </c>
+      <c r="H115" t="b">
+        <v>0</v>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Hungarian better (lower distance)</t>
+        </is>
+      </c>
+      <c r="J115" t="n">
+        <v>414</v>
+      </c>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>Not available in extracted results</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>RealEstate</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>GaussianCopula</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Gaussian Copula</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>16693.682733</v>
+      </c>
+      <c r="E116" t="n">
+        <v>16693.553751</v>
+      </c>
+      <c r="F116" t="n">
+        <v>-0.1289820000019972</v>
+      </c>
+      <c r="G116" t="n">
+        <v>-0.0007726395790847645</v>
+      </c>
+      <c r="H116" t="b">
+        <v>0</v>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Hungarian better (lower distance)</t>
+        </is>
+      </c>
+      <c r="J116" t="n">
+        <v>414</v>
+      </c>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>Not available in extracted results</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>RealEstate</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>WGAN_GP</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>WGAN-GP</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>1.4639</v>
+      </c>
+      <c r="E117" t="n">
+        <v>1.3965</v>
+      </c>
+      <c r="F117" t="n">
+        <v>-0.0673999999999999</v>
+      </c>
+      <c r="G117" t="n">
+        <v>-4.604139627023697</v>
+      </c>
+      <c r="H117" t="b">
+        <v>0</v>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Hungarian better (lower distance)</t>
+        </is>
+      </c>
+      <c r="J117" t="n">
+        <v>414</v>
+      </c>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>Not available in extracted results</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>RealEstate</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>CTABGAN</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>CTAB-GAN+</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>0.9013</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.8723</v>
+      </c>
+      <c r="F118" t="n">
+        <v>-0.02900000000000003</v>
+      </c>
+      <c r="G118" t="n">
+        <v>-3.217574614445804</v>
+      </c>
+      <c r="H118" t="b">
+        <v>0</v>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Hungarian better (lower distance)</t>
+        </is>
+      </c>
+      <c r="J118" t="n">
+        <v>414</v>
+      </c>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>Not available in extracted results</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>RealEstate</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>CTGAN</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>CTGAN</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>16692.881415</v>
+      </c>
+      <c r="E119" t="n">
+        <v>16692.752234</v>
+      </c>
+      <c r="F119" t="n">
+        <v>-0.1291810000002442</v>
+      </c>
+      <c r="G119" t="n">
+        <v>-0.0007738687934616484</v>
+      </c>
+      <c r="H119" t="b">
+        <v>0</v>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Hungarian better (lower distance)</t>
+        </is>
+      </c>
+      <c r="J119" t="n">
+        <v>414</v>
+      </c>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>Not available in extracted results</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>RealEstate</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.8743</v>
+      </c>
+      <c r="F120" t="n">
+        <v>-0.06320000000000003</v>
+      </c>
+      <c r="G120" t="n">
+        <v>-6.741333333333338</v>
+      </c>
+      <c r="H120" t="b">
+        <v>0</v>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Hungarian better (lower distance)</t>
+        </is>
+      </c>
+      <c r="J120" t="n">
+        <v>414</v>
+      </c>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>Not available in extracted results</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>RealEstate</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>CopulaGAN</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Copula GAN</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>16693.963602</v>
+      </c>
+      <c r="E121" t="n">
+        <v>16693.834433</v>
+      </c>
+      <c r="F121" t="n">
+        <v>-0.1291689999998198</v>
+      </c>
+      <c r="G121" t="n">
+        <v>-0.000773746745106985</v>
+      </c>
+      <c r="H121" t="b">
+        <v>0</v>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Hungarian better (lower distance)</t>
+        </is>
+      </c>
+      <c r="J121" t="n">
+        <v>414</v>
+      </c>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
         <is>
           <t>Not available in extracted results</t>
         </is>
@@ -5481,42 +6143,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Dataset</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Mean_Greedy</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Mean_Hungarian</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Mean_Diff</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>SD_Diff</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Median_Diff</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Pct_Hungarian_Better</t>
         </is>
@@ -5532,22 +6194,22 @@
         <v>8</v>
       </c>
       <c r="C2" t="n">
-        <v>31.430765625</v>
+        <v>48.86757725</v>
       </c>
       <c r="D2" t="n">
-        <v>20.17069725</v>
+        <v>48.63118925000001</v>
       </c>
       <c r="E2" t="n">
-        <v>-11.260068375</v>
+        <v>-0.2363880000000019</v>
       </c>
       <c r="F2" t="n">
-        <v>16.2465442080974</v>
+        <v>0.08640813201975285</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.2602000000000011</v>
+        <v>-0.254588000000004</v>
       </c>
       <c r="H2" t="n">
-        <v>87.5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3">
@@ -5588,22 +6250,22 @@
         <v>8</v>
       </c>
       <c r="C4" t="n">
-        <v>3.03801275</v>
+        <v>3.6481795</v>
       </c>
       <c r="D4" t="n">
-        <v>2.959367125</v>
+        <v>3.510309</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.078645625</v>
+        <v>-0.1378704999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4101146116332908</v>
+        <v>0.05981683194792013</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.1169999999999999</v>
+        <v>-0.1306554999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>87.5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5">
@@ -5641,22 +6303,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C6" t="n">
-        <v>3.80145</v>
+        <v>2.5798985</v>
       </c>
       <c r="D6" t="n">
-        <v>3.654325</v>
+        <v>2.364208125</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1471249999999996</v>
+        <v>-0.2156903749999998</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02449141005876742</v>
+        <v>0.0906875722276962</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.1457</v>
+        <v>-0.1793785</v>
       </c>
       <c r="H6" t="n">
         <v>100</v>
@@ -5669,22 +6331,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C7" t="n">
-        <v>3.5259</v>
+        <v>3.18677296584983</v>
       </c>
       <c r="D7" t="n">
-        <v>3.302575</v>
+        <v>2.890093722731807</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2233250000000001</v>
+        <v>-0.2966792431180231</v>
       </c>
       <c r="F7" t="n">
-        <v>0.08840932737368087</v>
+        <v>0.1367471562866815</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.2521</v>
+        <v>-0.2877500000000002</v>
       </c>
       <c r="H7" t="n">
         <v>100</v>
@@ -5756,22 +6418,22 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>2.094566</v>
+        <v>2.125616375</v>
       </c>
       <c r="D10" t="n">
-        <v>2.226736125</v>
+        <v>2.448392625</v>
       </c>
       <c r="E10" t="n">
-        <v>0.132170125</v>
+        <v>0.32277625</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5555226936402039</v>
+        <v>0.4996561257204084</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.04744999999999999</v>
+        <v>0.261393</v>
       </c>
       <c r="H10" t="n">
-        <v>62.5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11">
@@ -5809,22 +6471,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C12" t="n">
-        <v>3.38529225</v>
+        <v>2.655320625</v>
       </c>
       <c r="D12" t="n">
-        <v>3.23603125</v>
+        <v>2.508154375</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.149261</v>
+        <v>-0.14716625</v>
       </c>
       <c r="F12" t="n">
-        <v>0.01465472858841145</v>
+        <v>0.0121036916770995</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.1520505000000001</v>
+        <v>-0.1469435</v>
       </c>
       <c r="H12" t="n">
         <v>100</v>
@@ -5837,22 +6499,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C13" t="n">
-        <v>17.41407333333333</v>
+        <v>17.17639144998682</v>
       </c>
       <c r="D13" t="n">
-        <v>10.08670783333333</v>
+        <v>11.6102679145768</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.327365499999999</v>
+        <v>-5.56612353541001</v>
       </c>
       <c r="F13" t="n">
-        <v>13.10944605568217</v>
+        <v>11.54949334482794</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.2930000000000001</v>
+        <v>-0.2909491417978165</v>
       </c>
       <c r="H13" t="n">
         <v>100</v>
@@ -5957,47 +6619,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Generator</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Mean_Greedy</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Mean_Hungarian</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Mean_Diff</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>SD_Diff</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Median_Diff</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Pct_Hungarian_Better</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>GeneratorLabel</t>
         </is>
@@ -6043,25 +6705,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
-        <v>2987.938085583333</v>
+        <v>2391.542782609838</v>
       </c>
       <c r="D3" t="n">
-        <v>2983.307808583333</v>
+        <v>2389.263592576157</v>
       </c>
       <c r="E3" t="n">
-        <v>-4.630276999999796</v>
+        <v>-2.279190033680912</v>
       </c>
       <c r="F3" t="n">
-        <v>10.98503038147693</v>
+        <v>8.452418160755425</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.1200949999988943</v>
+        <v>-0.1413759999999997</v>
       </c>
       <c r="H3" t="n">
-        <v>83.33333333333334</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -6076,25 +6738,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C4" t="n">
-        <v>3185.11780175</v>
+        <v>2549.061096494515</v>
       </c>
       <c r="D4" t="n">
-        <v>3184.363785083333</v>
+        <v>2548.259643721199</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.7540166666668271</v>
+        <v>-0.8014527733160101</v>
       </c>
       <c r="F4" t="n">
-        <v>3.014286189764341</v>
+        <v>2.611169436185693</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.09607950000099841</v>
+        <v>-0.144391</v>
       </c>
       <c r="H4" t="n">
-        <v>75</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -6175,25 +6837,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C7" t="n">
-        <v>5709.058508636364</v>
+        <v>4191.713807989657</v>
       </c>
       <c r="D7" t="n">
-        <v>5706.362876545455</v>
+        <v>4191.588570994254</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.695632090909141</v>
+        <v>-0.1252369954025745</v>
       </c>
       <c r="F7" t="n">
-        <v>8.797150460289252</v>
+        <v>0.3208004624114607</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.129728</v>
+        <v>-0.2236070000000003</v>
       </c>
       <c r="H7" t="n">
-        <v>90.90909090909091</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -6241,25 +6903,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>6208.681919181819</v>
+        <v>4559.27508912777</v>
       </c>
       <c r="D9" t="n">
-        <v>6204.909631090909</v>
+        <v>4559.128942848288</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.772288090909288</v>
+        <v>-0.1461462794822696</v>
       </c>
       <c r="F9" t="n">
-        <v>11.60068913414866</v>
+        <v>0.303774030532835</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.2477780000000003</v>
+        <v>-0.2122929999999998</v>
       </c>
       <c r="H9" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -6282,77 +6944,77 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Scope</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Mean_Greedy</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Mean_Hungarian</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Mean_Diff_Hung_minus_Greedy</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>SD_Diff</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Median_Diff</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Pct_Hungarian_Better</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Statistic</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>p_value</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Effect_RankBiserial</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>p_holm</t>
         </is>
@@ -6370,25 +7032,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="D2" t="n">
-        <v>2521.258374783019</v>
+        <v>2228.795533469389</v>
       </c>
       <c r="E2" t="n">
-        <v>2519.904391066038</v>
+        <v>2228.311833309154</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.353983716981153</v>
+        <v>-0.4837001602352213</v>
       </c>
       <c r="G2" t="n">
-        <v>6.05895452607283</v>
+        <v>3.121977584066546</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.129184500000122</v>
+        <v>-0.1392589999999998</v>
       </c>
       <c r="I2" t="n">
-        <v>91.50943396226415</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -6396,13 +7058,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>4864</v>
+        <v>6435</v>
       </c>
       <c r="L2" t="n">
-        <v>3.197788125349079e-13</v>
+        <v>2.438031880918587e-16</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7153941103861752</v>
+        <v>0.7727272727272727</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -6410,7 +7072,7 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>3.197788125349079e-13</v>
+        <v>2.438031880918587e-16</v>
       </c>
     </row>
     <row r="3">
@@ -6480,25 +7142,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D4" t="n">
-        <v>2987.938085583333</v>
+        <v>2391.542782609838</v>
       </c>
       <c r="E4" t="n">
-        <v>2983.307808583333</v>
+        <v>2389.263592576157</v>
       </c>
       <c r="F4" t="n">
-        <v>-4.630276999999797</v>
+        <v>-2.279190033680912</v>
       </c>
       <c r="G4" t="n">
-        <v>10.98503038147693</v>
+        <v>8.452418160755425</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.1200949999988943</v>
+        <v>-0.1413759999999997</v>
       </c>
       <c r="I4" t="n">
-        <v>83.33333333333334</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -6506,13 +7168,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>66</v>
+        <v>104</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01708984375</v>
+        <v>0.005126953125</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6923076923076923</v>
+        <v>0.7333333333333334</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -6520,7 +7182,7 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>0.05126953125</v>
+        <v>0.013427734375</v>
       </c>
     </row>
     <row r="5">
@@ -6535,25 +7197,25 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D5" t="n">
-        <v>3185.11780175</v>
+        <v>2549.061096494515</v>
       </c>
       <c r="E5" t="n">
-        <v>3184.363785083333</v>
+        <v>2548.259643721199</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.7540166666668271</v>
+        <v>-0.8014527733160101</v>
       </c>
       <c r="G5" t="n">
-        <v>3.014286189764341</v>
+        <v>2.611169436185693</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.09607950000099841</v>
+        <v>-0.144391</v>
       </c>
       <c r="I5" t="n">
-        <v>75</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -6561,13 +7223,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>48</v>
+        <v>106</v>
       </c>
       <c r="L5" t="n">
-        <v>0.25927734375</v>
+        <v>0.00335693359375</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2307692307692308</v>
+        <v>0.7666666666666666</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -6575,7 +7237,7 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>0.25927734375</v>
+        <v>0.013427734375</v>
       </c>
     </row>
     <row r="6">
@@ -6630,7 +7292,7 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>0.00341796875</v>
+        <v>0.003425472838609693</v>
       </c>
     </row>
     <row r="7">
@@ -6685,7 +7347,7 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>0.00341796875</v>
+        <v>0.003425472838609693</v>
       </c>
     </row>
     <row r="8">
@@ -6700,25 +7362,25 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D8" t="n">
-        <v>5709.058508636364</v>
+        <v>4191.713807989657</v>
       </c>
       <c r="E8" t="n">
-        <v>5706.362876545455</v>
+        <v>4191.588570994254</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.695632090909141</v>
+        <v>-0.1252369954025745</v>
       </c>
       <c r="G8" t="n">
-        <v>8.797150460289252</v>
+        <v>0.3208004624114607</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.129728</v>
+        <v>-0.2236070000000003</v>
       </c>
       <c r="I8" t="n">
-        <v>90.90909090909091</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -6726,13 +7388,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>56</v>
+        <v>105</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02099609375</v>
+        <v>0.004180908203125</v>
       </c>
       <c r="M8" t="n">
-        <v>0.696969696969697</v>
+        <v>0.75</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -6740,7 +7402,7 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>0.05126953125</v>
+        <v>0.013427734375</v>
       </c>
     </row>
     <row r="9">
@@ -6795,7 +7457,7 @@
         </is>
       </c>
       <c r="O9" t="n">
-        <v>0.00341796875</v>
+        <v>0.003425472838609693</v>
       </c>
     </row>
     <row r="10">
@@ -6810,25 +7472,25 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D10" t="n">
-        <v>6208.681919181819</v>
+        <v>4559.27508912777</v>
       </c>
       <c r="E10" t="n">
-        <v>6204.909631090909</v>
+        <v>4559.128942848287</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.772288090909288</v>
+        <v>-0.1461462794822696</v>
       </c>
       <c r="G10" t="n">
-        <v>11.60068913414865</v>
+        <v>0.303774030532835</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2477780000000003</v>
+        <v>-0.2122929999999998</v>
       </c>
       <c r="I10" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -6836,13 +7498,13 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>66</v>
+        <v>105</v>
       </c>
       <c r="L10" t="n">
-        <v>0.00048828125</v>
+        <v>0.004180908203125</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -6850,7 +7512,7 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>0.00341796875</v>
+        <v>0.013427734375</v>
       </c>
     </row>
     <row r="11">
@@ -6868,22 +7530,22 @@
         <v>8</v>
       </c>
       <c r="D11" t="n">
-        <v>31.430765625</v>
+        <v>48.86757725000001</v>
       </c>
       <c r="E11" t="n">
-        <v>20.17069725</v>
+        <v>48.63118925</v>
       </c>
       <c r="F11" t="n">
-        <v>-11.260068375</v>
+        <v>-0.2363880000000019</v>
       </c>
       <c r="G11" t="n">
-        <v>16.2465442080974</v>
+        <v>0.08640813201975285</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.2602000000000011</v>
+        <v>-0.254588000000004</v>
       </c>
       <c r="I11" t="n">
-        <v>87.5</v>
+        <v>100</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -6891,13 +7553,13 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0390625</v>
+        <v>0.00390625</v>
       </c>
       <c r="M11" t="n">
-        <v>0.7222222222222223</v>
+        <v>1</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -6905,7 +7567,7 @@
         </is>
       </c>
       <c r="O11" t="n">
-        <v>0.234375</v>
+        <v>0.05859375</v>
       </c>
     </row>
     <row r="12">
@@ -6978,22 +7640,22 @@
         <v>8</v>
       </c>
       <c r="D13" t="n">
-        <v>3.03801275</v>
+        <v>3.6481795</v>
       </c>
       <c r="E13" t="n">
-        <v>2.959367125</v>
+        <v>3.510309</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.078645625</v>
+        <v>-0.1378704999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4101146116332908</v>
+        <v>0.05981683194792013</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.1169999999999999</v>
+        <v>-0.1306554999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>87.5</v>
+        <v>100</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -7001,13 +7663,13 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="L13" t="n">
-        <v>0.09765625</v>
+        <v>0.00390625</v>
       </c>
       <c r="M13" t="n">
-        <v>0.5555555555555556</v>
+        <v>1</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -7015,7 +7677,7 @@
         </is>
       </c>
       <c r="O13" t="n">
-        <v>0.3125</v>
+        <v>0.05859375</v>
       </c>
     </row>
     <row r="14">
@@ -7085,22 +7747,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D15" t="n">
-        <v>3.80145</v>
+        <v>2.5798985</v>
       </c>
       <c r="E15" t="n">
-        <v>3.654325</v>
+        <v>2.364208125</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1471249999999996</v>
+        <v>-0.2156903749999998</v>
       </c>
       <c r="G15" t="n">
-        <v>0.02449141005876742</v>
+        <v>0.09068757222769619</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.1457</v>
+        <v>-0.1793785</v>
       </c>
       <c r="I15" t="n">
         <v>100</v>
@@ -7111,10 +7773,10 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0625</v>
+        <v>0.00390625</v>
       </c>
       <c r="M15" t="n">
         <v>1</v>
@@ -7125,7 +7787,7 @@
         </is>
       </c>
       <c r="O15" t="n">
-        <v>0.3125</v>
+        <v>0.05859375</v>
       </c>
     </row>
     <row r="16">
@@ -7140,22 +7802,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D16" t="n">
-        <v>3.5259</v>
+        <v>3.18677296584983</v>
       </c>
       <c r="E16" t="n">
-        <v>3.302575</v>
+        <v>2.890093722731807</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2233250000000001</v>
+        <v>-0.2966792431180231</v>
       </c>
       <c r="G16" t="n">
-        <v>0.08840932737368087</v>
+        <v>0.1367471562866815</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.2521</v>
+        <v>-0.2877500000000002</v>
       </c>
       <c r="I16" t="n">
         <v>100</v>
@@ -7166,10 +7828,10 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0625</v>
+        <v>0.00390625</v>
       </c>
       <c r="M16" t="n">
         <v>1</v>
@@ -7180,7 +7842,7 @@
         </is>
       </c>
       <c r="O16" t="n">
-        <v>0.3125</v>
+        <v>0.05859375</v>
       </c>
     </row>
     <row r="17">
@@ -7308,22 +7970,22 @@
         <v>8</v>
       </c>
       <c r="D19" t="n">
-        <v>2.094566</v>
+        <v>2.125616375</v>
       </c>
       <c r="E19" t="n">
-        <v>2.226736125</v>
+        <v>2.448392625</v>
       </c>
       <c r="F19" t="n">
-        <v>0.132170125</v>
+        <v>0.32277625</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5555226936402039</v>
+        <v>0.4996561257204084</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.04744999999999999</v>
+        <v>0.261393</v>
       </c>
       <c r="I19" t="n">
-        <v>62.5</v>
+        <v>50</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -7331,13 +7993,13 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="L19" t="n">
-        <v>0.62890625</v>
+        <v>0.875</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1111111111111112</v>
+        <v>-0.4444444444444444</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -7345,7 +8007,7 @@
         </is>
       </c>
       <c r="O19" t="n">
-        <v>0.62890625</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="20">
@@ -7400,7 +8062,7 @@
         </is>
       </c>
       <c r="O20" t="n">
-        <v>0.10546875</v>
+        <v>0.05859375</v>
       </c>
     </row>
     <row r="21">
@@ -7415,22 +8077,22 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D21" t="n">
-        <v>3.38529225</v>
+        <v>2.655320625</v>
       </c>
       <c r="E21" t="n">
-        <v>3.23603125</v>
+        <v>2.508154375</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.149261</v>
+        <v>-0.14716625</v>
       </c>
       <c r="G21" t="n">
-        <v>0.01465472858841145</v>
+        <v>0.01210369167709952</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.1520505000000001</v>
+        <v>-0.1469435</v>
       </c>
       <c r="I21" t="n">
         <v>100</v>
@@ -7441,10 +8103,10 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0625</v>
+        <v>0.00390625</v>
       </c>
       <c r="M21" t="n">
         <v>1</v>
@@ -7455,7 +8117,7 @@
         </is>
       </c>
       <c r="O21" t="n">
-        <v>0.3125</v>
+        <v>0.05859375</v>
       </c>
     </row>
     <row r="22">
@@ -7470,22 +8132,22 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D22" t="n">
-        <v>17.41407333333333</v>
+        <v>17.17639144998682</v>
       </c>
       <c r="E22" t="n">
-        <v>10.08670783333333</v>
+        <v>11.6102679145768</v>
       </c>
       <c r="F22" t="n">
-        <v>-7.327365499999999</v>
+        <v>-5.56612353541001</v>
       </c>
       <c r="G22" t="n">
-        <v>13.10944605568216</v>
+        <v>11.54949334482794</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.2930000000000001</v>
+        <v>-0.2909491417978165</v>
       </c>
       <c r="I22" t="n">
         <v>100</v>
@@ -7496,10 +8158,10 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="L22" t="n">
-        <v>0.015625</v>
+        <v>0.00390625</v>
       </c>
       <c r="M22" t="n">
         <v>1</v>
@@ -7510,7 +8172,7 @@
         </is>
       </c>
       <c r="O22" t="n">
-        <v>0.125</v>
+        <v>0.05859375</v>
       </c>
     </row>
     <row r="23">
@@ -7620,7 +8282,7 @@
         </is>
       </c>
       <c r="O24" t="n">
-        <v>0.21875</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="25">
@@ -7689,265 +8351,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>dataset</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>generator</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>reason</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Bank</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>CTGAN</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>missing Greedy and/or Hungarian Mahalanobis mean in extracted summary</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Bank</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>CopulaGAN</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>missing Greedy and/or Hungarian Mahalanobis mean in extracted summary</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Bank</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>TVAE</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>missing Greedy and/or Hungarian Mahalanobis mean in extracted summary</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Bank</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>GaussianCopula</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>missing Greedy and/or Hungarian Mahalanobis mean in extracted summary</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Wine</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>CTGAN</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>incomplete Mahalanobis methods available: ['Hungarian']</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Wine</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>CopulaGAN</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>incomplete Mahalanobis methods available: ['Hungarian']</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Wine</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>TVAE</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>incomplete Mahalanobis methods available: ['Hungarian']</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Wine</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>GaussianCopula</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>incomplete Mahalanobis methods available: ['Hungarian']</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>OnlineShop</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>CTGAN</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>incomplete Mahalanobis methods available: ['Hungarian']</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>OnlineShop</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>CopulaGAN</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>incomplete Mahalanobis methods available: ['Hungarian']</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>OnlineShop</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>TVAE</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>incomplete Mahalanobis methods available: ['Hungarian']</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>OnlineShop</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>GaussianCopula</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>incomplete Mahalanobis methods available: ['Hungarian']</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>AirQuality</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>CTGAN</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>incomplete Mahalanobis methods available: ['Hungarian']</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>AirQuality</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>CopulaGAN</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>incomplete Mahalanobis methods available: ['Hungarian']</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7962,12 +8368,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
@@ -7981,7 +8387,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>C:\Users\Gopi.Battineni\OneDrive - University of Limerick\Desktop\SYNTH\SYNTH_FRAMEWORK\mapping study graphs\extracted_results\hungarian_vs_greedy_summary.csv</t>
+          <t>/home/gopi_b/SYNTH_FRAMEWORK_NEW/mapping study graphs/extracted_results/hungarian_vs_greedy_summary.csv</t>
         </is>
       </c>
     </row>
@@ -7993,7 +8399,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>C:\Users\Gopi.Battineni\OneDrive - University of Limerick\Desktop\SYNTH\SYNTH_FRAMEWORK\mapping study graphs\extracted_results\mahalanobis_distance_results.csv</t>
+          <t>/home/gopi_b/SYNTH_FRAMEWORK_NEW/mapping study graphs/extracted_results/mahalanobis_distance_results.csv</t>
         </is>
       </c>
     </row>
@@ -8016,7 +8422,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>106</v>
+        <v>120</v>
       </c>
     </row>
     <row r="6">
@@ -8026,7 +8432,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">

--- a/mapping study graphs/outputs/mahalanobis_greedy_vs_hungarian/tables/mahalanobis_greedy_vs_hungarian_tables.xlsx
+++ b/mapping study graphs/outputs/mahalanobis_greedy_vs_hungarian/tables/mahalanobis_greedy_vs_hungarian_tables.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M121"/>
+  <dimension ref="A1:M115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2435,25 +2435,25 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>TVAE</t>
+          <t>WGAN_GP</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>TVAE</t>
+          <t>WGAN-GP</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>2.550131147570549</v>
+        <v>3.6759</v>
       </c>
       <c r="E43" t="n">
-        <v>2.062422642354435</v>
+        <v>3.3891</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.4877085052161139</v>
+        <v>-0.2867999999999999</v>
       </c>
       <c r="G43" t="n">
-        <v>-19.12484013540804</v>
+        <v>-7.802170896923201</v>
       </c>
       <c r="H43" t="b">
         <v>0</v>
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="J43" t="n">
-        <v>6497</v>
+        <v>1000</v>
       </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
@@ -2482,25 +2482,25 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>GaussianCopula</t>
+          <t>CTABGAN</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Gaussian Copula</t>
+          <t>CTAB-GAN+</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>2.167596417725627</v>
+        <v>3.3377</v>
       </c>
       <c r="E44" t="n">
-        <v>2.011109817987401</v>
+        <v>3.1203</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.1564865997382263</v>
+        <v>-0.2174</v>
       </c>
       <c r="G44" t="n">
-        <v>-7.219360507267377</v>
+        <v>-6.513467357761334</v>
       </c>
       <c r="H44" t="b">
         <v>0</v>
@@ -2511,7 +2511,7 @@
         </is>
       </c>
       <c r="J44" t="n">
-        <v>6497</v>
+        <v>1000</v>
       </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
@@ -2529,25 +2529,25 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>WGAN_GP</t>
+          <t>TabDDPM</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>WGAN-GP</t>
+          <t>TabDDPM</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>3.6759</v>
+        <v>5.4729</v>
       </c>
       <c r="E45" t="n">
-        <v>3.3891</v>
+        <v>5.1842</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.2867999999999999</v>
+        <v>-0.2887000000000004</v>
       </c>
       <c r="G45" t="n">
-        <v>-7.802170896923201</v>
+        <v>-5.275082680114754</v>
       </c>
       <c r="H45" t="b">
         <v>0</v>
@@ -2571,30 +2571,30 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Wine</t>
+          <t>CDC</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CTABGAN</t>
+          <t>ForestDiffusion</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CTAB-GAN+</t>
+          <t>Forest Diffusion</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>3.3377</v>
+        <v>2.7934</v>
       </c>
       <c r="E46" t="n">
-        <v>3.1203</v>
+        <v>2.6942</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.2174</v>
+        <v>-0.09920000000000018</v>
       </c>
       <c r="G46" t="n">
-        <v>-6.513467357761334</v>
+        <v>-3.551227894322337</v>
       </c>
       <c r="H46" t="b">
         <v>0</v>
@@ -2618,30 +2618,30 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Wine</t>
+          <t>CDC</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CTGAN</t>
+          <t>TVAE</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CTGAN</t>
+          <t>TVAE</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>3.501071108209549</v>
+        <v>3.0372</v>
       </c>
       <c r="E47" t="n">
-        <v>3.096475460767122</v>
+        <v>2.801934</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.4045956474424273</v>
+        <v>-0.2352659999999998</v>
       </c>
       <c r="G47" t="n">
-        <v>-11.55633904417719</v>
+        <v>-7.74614776768075</v>
       </c>
       <c r="H47" t="b">
         <v>0</v>
@@ -2652,7 +2652,7 @@
         </is>
       </c>
       <c r="J47" t="n">
-        <v>6497</v>
+        <v>5000</v>
       </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
@@ -2665,30 +2665,30 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Wine</t>
+          <t>CDC</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>TabDDPM</t>
+          <t>GaussianCopula</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>TabDDPM</t>
+          <t>Gaussian Copula</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>5.4729</v>
+        <v>3.956109</v>
       </c>
       <c r="E48" t="n">
-        <v>5.1842</v>
+        <v>3.569087</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.2887000000000004</v>
+        <v>-0.387022</v>
       </c>
       <c r="G48" t="n">
-        <v>-5.275082680114754</v>
+        <v>-9.782895264008145</v>
       </c>
       <c r="H48" t="b">
         <v>0</v>
@@ -2699,7 +2699,7 @@
         </is>
       </c>
       <c r="J48" t="n">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
@@ -2712,30 +2712,30 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Wine</t>
+          <t>CDC</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CopulaGAN</t>
+          <t>WGAN_GP</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Copula GAN</t>
+          <t>WGAN-GP</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>3.171785053292916</v>
+        <v>3.9642</v>
       </c>
       <c r="E49" t="n">
-        <v>2.740441860745499</v>
+        <v>3.8121</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.4313431925474172</v>
+        <v>-0.1520999999999999</v>
       </c>
       <c r="G49" t="n">
-        <v>-13.59938284908685</v>
+        <v>-3.836839715453304</v>
       </c>
       <c r="H49" t="b">
         <v>0</v>
@@ -2746,7 +2746,7 @@
         </is>
       </c>
       <c r="J49" t="n">
-        <v>6497</v>
+        <v>1000</v>
       </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
@@ -2764,25 +2764,25 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ForestDiffusion</t>
+          <t>CTABGAN</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Forest Diffusion</t>
+          <t>CTAB-GAN+</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>2.7934</v>
+        <v>6.856</v>
       </c>
       <c r="E50" t="n">
-        <v>2.6942</v>
+        <v>6.7014</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.09920000000000018</v>
+        <v>-0.1546000000000003</v>
       </c>
       <c r="G50" t="n">
-        <v>-3.551227894322337</v>
+        <v>-2.254959159859981</v>
       </c>
       <c r="H50" t="b">
         <v>0</v>
@@ -2811,25 +2811,25 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>TVAE</t>
+          <t>CTGAN</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>TVAE</t>
+          <t>CTGAN</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>3.0372</v>
+        <v>3.446302</v>
       </c>
       <c r="E51" t="n">
-        <v>2.801934</v>
+        <v>3.072402</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.2352659999999998</v>
+        <v>-0.3739000000000003</v>
       </c>
       <c r="G51" t="n">
-        <v>-7.74614776768075</v>
+        <v>-10.84931036223756</v>
       </c>
       <c r="H51" t="b">
         <v>0</v>
@@ -2858,25 +2858,25 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>GaussianCopula</t>
+          <t>TabDDPM</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Gaussian Copula</t>
+          <t>TabDDPM</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>3.956109</v>
+        <v>8.513500000000001</v>
       </c>
       <c r="E52" t="n">
-        <v>3.569087</v>
+        <v>8.3148</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.387022</v>
+        <v>-0.1987000000000005</v>
       </c>
       <c r="G52" t="n">
-        <v>-9.782895264008145</v>
+        <v>-2.333940212603518</v>
       </c>
       <c r="H52" t="b">
         <v>0</v>
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="J52" t="n">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
@@ -2905,25 +2905,25 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>WGAN_GP</t>
+          <t>CopulaGAN</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>WGAN-GP</t>
+          <t>Copula GAN</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>3.9642</v>
+        <v>3.788867</v>
       </c>
       <c r="E53" t="n">
-        <v>3.8121</v>
+        <v>3.345442</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.1520999999999999</v>
+        <v>-0.4434250000000004</v>
       </c>
       <c r="G53" t="n">
-        <v>-3.836839715453304</v>
+        <v>-11.70336673206002</v>
       </c>
       <c r="H53" t="b">
         <v>0</v>
@@ -2934,7 +2934,7 @@
         </is>
       </c>
       <c r="J53" t="n">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
@@ -2947,30 +2947,30 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>CDC</t>
+          <t>Mushroom</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CTABGAN</t>
+          <t>ForestDiffusion</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CTAB-GAN+</t>
+          <t>Forest Diffusion</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>6.856</v>
+        <v>0.6321</v>
       </c>
       <c r="E54" t="n">
-        <v>6.7014</v>
+        <v>0.5276</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.1546000000000003</v>
+        <v>-0.1045</v>
       </c>
       <c r="G54" t="n">
-        <v>-2.254959159859981</v>
+        <v>-16.53219427305806</v>
       </c>
       <c r="H54" t="b">
         <v>0</v>
@@ -2994,30 +2994,30 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>CDC</t>
+          <t>Mushroom</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CTGAN</t>
+          <t>TVAE</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CTGAN</t>
+          <t>TVAE</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>3.446302</v>
+        <v>0.544045</v>
       </c>
       <c r="E55" t="n">
-        <v>3.072402</v>
+        <v>0.433018</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.3739000000000003</v>
+        <v>-0.111027</v>
       </c>
       <c r="G55" t="n">
-        <v>-10.84931036223756</v>
+        <v>-20.40768686413807</v>
       </c>
       <c r="H55" t="b">
         <v>0</v>
@@ -3028,7 +3028,7 @@
         </is>
       </c>
       <c r="J55" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
@@ -3041,30 +3041,30 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CDC</t>
+          <t>Mushroom</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>TabDDPM</t>
+          <t>GaussianCopula</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>TabDDPM</t>
+          <t>Gaussian Copula</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>8.513500000000001</v>
+        <v>0.538448</v>
       </c>
       <c r="E56" t="n">
-        <v>8.3148</v>
+        <v>0.394057</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.1987000000000005</v>
+        <v>-0.144391</v>
       </c>
       <c r="G56" t="n">
-        <v>-2.333940212603518</v>
+        <v>-26.81614566309096</v>
       </c>
       <c r="H56" t="b">
         <v>0</v>
@@ -3075,7 +3075,7 @@
         </is>
       </c>
       <c r="J56" t="n">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
@@ -3088,30 +3088,30 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>CDC</t>
+          <t>Mushroom</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CopulaGAN</t>
+          <t>WGAN_GP</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Copula GAN</t>
+          <t>WGAN-GP</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>3.788867</v>
+        <v>1.1701</v>
       </c>
       <c r="E57" t="n">
-        <v>3.345442</v>
+        <v>1.0407</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.4434250000000004</v>
+        <v>-0.1294</v>
       </c>
       <c r="G57" t="n">
-        <v>-11.70336673206002</v>
+        <v>-11.05888385608067</v>
       </c>
       <c r="H57" t="b">
         <v>0</v>
@@ -3122,7 +3122,7 @@
         </is>
       </c>
       <c r="J57" t="n">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
@@ -3140,25 +3140,25 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ForestDiffusion</t>
+          <t>CTABGAN</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Forest Diffusion</t>
+          <t>CTAB-GAN+</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.6321</v>
+        <v>1.9831</v>
       </c>
       <c r="E58" t="n">
-        <v>0.5276</v>
+        <v>1.8176</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.1045</v>
+        <v>-0.1655</v>
       </c>
       <c r="G58" t="n">
-        <v>-16.53219427305806</v>
+        <v>-8.345519640966163</v>
       </c>
       <c r="H58" t="b">
         <v>0</v>
@@ -3187,25 +3187,25 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>TVAE</t>
+          <t>CTGAN</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>TVAE</t>
+          <t>CTGAN</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>0.544045</v>
+        <v>0.615897</v>
       </c>
       <c r="E59" t="n">
-        <v>0.433018</v>
+        <v>0.486169</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.111027</v>
+        <v>-0.129728</v>
       </c>
       <c r="G59" t="n">
-        <v>-20.40768686413807</v>
+        <v>-21.06326220130964</v>
       </c>
       <c r="H59" t="b">
         <v>0</v>
@@ -3234,25 +3234,25 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>GaussianCopula</t>
+          <t>TabDDPM</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Gaussian Copula</t>
+          <t>TabDDPM</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>0.538448</v>
+        <v>9.373900000000001</v>
       </c>
       <c r="E60" t="n">
-        <v>0.394057</v>
+        <v>9.2433</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.144391</v>
+        <v>-0.1306000000000012</v>
       </c>
       <c r="G60" t="n">
-        <v>-26.81614566309096</v>
+        <v>-1.393230139002989</v>
       </c>
       <c r="H60" t="b">
         <v>0</v>
@@ -3263,7 +3263,7 @@
         </is>
       </c>
       <c r="J60" t="n">
-        <v>10000</v>
+        <v>1000</v>
       </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
@@ -3281,25 +3281,25 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>WGAN_GP</t>
+          <t>CopulaGAN</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>WGAN-GP</t>
+          <t>Copula GAN</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1.1701</v>
+        <v>0.698264</v>
       </c>
       <c r="E61" t="n">
-        <v>1.0407</v>
+        <v>0.539467</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.1294</v>
+        <v>-0.158797</v>
       </c>
       <c r="G61" t="n">
-        <v>-11.05888385608067</v>
+        <v>-22.74168509331713</v>
       </c>
       <c r="H61" t="b">
         <v>0</v>
@@ -3310,7 +3310,7 @@
         </is>
       </c>
       <c r="J61" t="n">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
@@ -3323,30 +3323,30 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Mushroom</t>
+          <t>MAGIC</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CTABGAN</t>
+          <t>ForestDiffusion</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>CTAB-GAN+</t>
+          <t>Forest Diffusion</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1.9831</v>
+        <v>1.432</v>
       </c>
       <c r="E62" t="n">
-        <v>1.8176</v>
+        <v>1.3078</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.1655</v>
+        <v>-0.1241999999999999</v>
       </c>
       <c r="G62" t="n">
-        <v>-8.345519640966163</v>
+        <v>-8.67318435754189</v>
       </c>
       <c r="H62" t="b">
         <v>0</v>
@@ -3370,41 +3370,41 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Mushroom</t>
+          <t>MAGIC</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CTGAN</t>
+          <t>TVAE</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>CTGAN</t>
+          <t>TVAE</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>0.615897</v>
+        <v>1.25837</v>
       </c>
       <c r="E63" t="n">
-        <v>0.486169</v>
+        <v>2.000846</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.129728</v>
+        <v>0.7424760000000001</v>
       </c>
       <c r="G63" t="n">
-        <v>-21.06326220130964</v>
+        <v>59.00299593919119</v>
       </c>
       <c r="H63" t="b">
         <v>0</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Hungarian better (lower distance)</t>
+          <t>Hungarian worse (higher distance)</t>
         </is>
       </c>
       <c r="J63" t="n">
-        <v>10000</v>
+        <v>19020</v>
       </c>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
@@ -3417,41 +3417,41 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Mushroom</t>
+          <t>MAGIC</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>TabDDPM</t>
+          <t>GaussianCopula</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>TabDDPM</t>
+          <t>Gaussian Copula</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>9.373900000000001</v>
+        <v>1.948976</v>
       </c>
       <c r="E64" t="n">
-        <v>9.2433</v>
+        <v>2.490962</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.1306000000000012</v>
+        <v>0.5419860000000001</v>
       </c>
       <c r="G64" t="n">
-        <v>-1.393230139002989</v>
+        <v>27.80875700880873</v>
       </c>
       <c r="H64" t="b">
         <v>0</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Hungarian better (lower distance)</t>
+          <t>Hungarian worse (higher distance)</t>
         </is>
       </c>
       <c r="J64" t="n">
-        <v>1000</v>
+        <v>19020</v>
       </c>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
@@ -3464,30 +3464,30 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Mushroom</t>
+          <t>MAGIC</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CopulaGAN</t>
+          <t>WGAN_GP</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Copula GAN</t>
+          <t>WGAN-GP</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>0.698264</v>
+        <v>1.209</v>
       </c>
       <c r="E65" t="n">
-        <v>0.539467</v>
+        <v>1.1898</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.158797</v>
+        <v>-0.01920000000000011</v>
       </c>
       <c r="G65" t="n">
-        <v>-22.74168509331713</v>
+        <v>-1.588089330024823</v>
       </c>
       <c r="H65" t="b">
         <v>0</v>
@@ -3498,7 +3498,7 @@
         </is>
       </c>
       <c r="J65" t="n">
-        <v>10000</v>
+        <v>1000</v>
       </c>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
@@ -3516,25 +3516,25 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ForestDiffusion</t>
+          <t>CTABGAN</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Forest Diffusion</t>
+          <t>CTAB-GAN+</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1.432</v>
+        <v>1.9498</v>
       </c>
       <c r="E66" t="n">
-        <v>1.3078</v>
+        <v>1.8741</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.1241999999999999</v>
+        <v>-0.07569999999999988</v>
       </c>
       <c r="G66" t="n">
-        <v>-8.67318435754189</v>
+        <v>-3.882449481998147</v>
       </c>
       <c r="H66" t="b">
         <v>0</v>
@@ -3563,25 +3563,25 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>TVAE</t>
+          <t>CTGAN</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>TVAE</t>
+          <t>CTGAN</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1.25837</v>
+        <v>2.43384</v>
       </c>
       <c r="E67" t="n">
-        <v>2.000846</v>
+        <v>3.383397</v>
       </c>
       <c r="F67" t="n">
-        <v>0.7424760000000001</v>
+        <v>0.949557</v>
       </c>
       <c r="G67" t="n">
-        <v>59.00299593919119</v>
+        <v>39.01476678828518</v>
       </c>
       <c r="H67" t="b">
         <v>0</v>
@@ -3610,36 +3610,36 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>GaussianCopula</t>
+          <t>TabDDPM</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Gaussian Copula</t>
+          <t>TabDDPM</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1.948976</v>
+        <v>4.5721</v>
       </c>
       <c r="E68" t="n">
-        <v>2.490962</v>
+        <v>4.2848</v>
       </c>
       <c r="F68" t="n">
-        <v>0.5419860000000001</v>
+        <v>-0.2873000000000001</v>
       </c>
       <c r="G68" t="n">
-        <v>27.80875700880873</v>
+        <v>-6.283764572078478</v>
       </c>
       <c r="H68" t="b">
         <v>0</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Hungarian worse (higher distance)</t>
+          <t>Hungarian better (lower distance)</t>
         </is>
       </c>
       <c r="J68" t="n">
-        <v>19020</v>
+        <v>1000</v>
       </c>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
@@ -3657,36 +3657,36 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>WGAN_GP</t>
+          <t>CopulaGAN</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>WGAN-GP</t>
+          <t>Copula GAN</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1.209</v>
+        <v>2.200845</v>
       </c>
       <c r="E69" t="n">
-        <v>1.1898</v>
+        <v>3.055436</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.01920000000000011</v>
+        <v>0.8545909999999997</v>
       </c>
       <c r="G69" t="n">
-        <v>-1.588089330024823</v>
+        <v>38.83013115417031</v>
       </c>
       <c r="H69" t="b">
         <v>0</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Hungarian better (lower distance)</t>
+          <t>Hungarian worse (higher distance)</t>
         </is>
       </c>
       <c r="J69" t="n">
-        <v>1000</v>
+        <v>19020</v>
       </c>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
@@ -3699,30 +3699,30 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>MAGIC</t>
+          <t>Metro</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>CTABGAN</t>
+          <t>ForestDiffusion</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>CTAB-GAN+</t>
+          <t>Forest Diffusion</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1.9498</v>
+        <v>0.35574</v>
       </c>
       <c r="E70" t="n">
-        <v>1.8741</v>
+        <v>0.297551</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.07569999999999988</v>
+        <v>-0.05818899999999999</v>
       </c>
       <c r="G70" t="n">
-        <v>-3.882449481998147</v>
+        <v>-16.35717096756058</v>
       </c>
       <c r="H70" t="b">
         <v>0</v>
@@ -3746,30 +3746,30 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>MAGIC</t>
+          <t>Metro</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>CTGAN</t>
+          <t>TVAE</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>CTGAN</t>
+          <t>TVAE</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>2.43384</v>
+        <v>0.258434</v>
       </c>
       <c r="E71" t="n">
-        <v>3.383397</v>
+        <v>0.291262</v>
       </c>
       <c r="F71" t="n">
-        <v>0.949557</v>
+        <v>0.03282800000000002</v>
       </c>
       <c r="G71" t="n">
-        <v>39.01476678828518</v>
+        <v>12.70266296230373</v>
       </c>
       <c r="H71" t="b">
         <v>0</v>
@@ -3780,7 +3780,7 @@
         </is>
       </c>
       <c r="J71" t="n">
-        <v>19020</v>
+        <v>5000</v>
       </c>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
@@ -3793,30 +3793,30 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>MAGIC</t>
+          <t>Metro</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>TabDDPM</t>
+          <t>GaussianCopula</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>TabDDPM</t>
+          <t>Gaussian Copula</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>4.5721</v>
+        <v>27.853218</v>
       </c>
       <c r="E72" t="n">
-        <v>4.2848</v>
+        <v>27.790041</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.2873000000000001</v>
+        <v>-0.06317699999999959</v>
       </c>
       <c r="G72" t="n">
-        <v>-6.283764572078478</v>
+        <v>-0.2268211881298585</v>
       </c>
       <c r="H72" t="b">
         <v>0</v>
@@ -3827,7 +3827,7 @@
         </is>
       </c>
       <c r="J72" t="n">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
@@ -3840,41 +3840,41 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>MAGIC</t>
+          <t>Metro</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>CopulaGAN</t>
+          <t>WGAN_GP</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Copula GAN</t>
+          <t>WGAN-GP</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>2.200845</v>
+        <v>1.498572</v>
       </c>
       <c r="E73" t="n">
-        <v>3.055436</v>
+        <v>1.410562</v>
       </c>
       <c r="F73" t="n">
-        <v>0.8545909999999997</v>
+        <v>-0.08800999999999992</v>
       </c>
       <c r="G73" t="n">
-        <v>38.83013115417031</v>
+        <v>-5.872924357321497</v>
       </c>
       <c r="H73" t="b">
         <v>0</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Hungarian worse (higher distance)</t>
+          <t>Hungarian better (lower distance)</t>
         </is>
       </c>
       <c r="J73" t="n">
-        <v>19020</v>
+        <v>1000</v>
       </c>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
@@ -3892,25 +3892,25 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ForestDiffusion</t>
+          <t>CTABGAN</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Forest Diffusion</t>
+          <t>CTAB-GAN+</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>0.35574</v>
+        <v>1.607389</v>
       </c>
       <c r="E74" t="n">
-        <v>0.297551</v>
+        <v>1.468671</v>
       </c>
       <c r="F74" t="n">
-        <v>-0.05818899999999999</v>
+        <v>-0.1387179999999999</v>
       </c>
       <c r="G74" t="n">
-        <v>-16.35717096756058</v>
+        <v>-8.630020486640129</v>
       </c>
       <c r="H74" t="b">
         <v>0</v>
@@ -3939,32 +3939,32 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>TVAE</t>
+          <t>CTGAN</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>TVAE</t>
+          <t>CTGAN</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>0.258434</v>
+        <v>0.431625</v>
       </c>
       <c r="E75" t="n">
-        <v>0.291262</v>
+        <v>0.399805</v>
       </c>
       <c r="F75" t="n">
-        <v>0.03282800000000002</v>
+        <v>-0.03181999999999996</v>
       </c>
       <c r="G75" t="n">
-        <v>12.70266296230373</v>
+        <v>-7.372140167969873</v>
       </c>
       <c r="H75" t="b">
         <v>0</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Hungarian worse (higher distance)</t>
+          <t>Hungarian better (lower distance)</t>
         </is>
       </c>
       <c r="J75" t="n">
@@ -3986,25 +3986,25 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>GaussianCopula</t>
+          <t>TabDDPM</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Gaussian Copula</t>
+          <t>TabDDPM</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>27.853218</v>
+        <v>13.596022</v>
       </c>
       <c r="E76" t="n">
-        <v>27.790041</v>
+        <v>13.548747</v>
       </c>
       <c r="F76" t="n">
-        <v>-0.06317699999999959</v>
+        <v>-0.04727499999999907</v>
       </c>
       <c r="G76" t="n">
-        <v>-0.2268211881298585</v>
+        <v>-0.3477119998776044</v>
       </c>
       <c r="H76" t="b">
         <v>0</v>
@@ -4015,7 +4015,7 @@
         </is>
       </c>
       <c r="J76" t="n">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
@@ -4033,25 +4033,25 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>WGAN_GP</t>
+          <t>CopulaGAN</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>WGAN-GP</t>
+          <t>Copula GAN</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1.498572</v>
+        <v>0.587039</v>
       </c>
       <c r="E77" t="n">
-        <v>1.410562</v>
+        <v>0.482782</v>
       </c>
       <c r="F77" t="n">
-        <v>-0.08800999999999992</v>
+        <v>-0.104257</v>
       </c>
       <c r="G77" t="n">
-        <v>-5.872924357321497</v>
+        <v>-17.75980812177726</v>
       </c>
       <c r="H77" t="b">
         <v>0</v>
@@ -4062,7 +4062,7 @@
         </is>
       </c>
       <c r="J77" t="n">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
@@ -4075,30 +4075,30 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Metro</t>
+          <t>OnlineShop</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>CTABGAN</t>
+          <t>ForestDiffusion</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>CTAB-GAN+</t>
+          <t>Forest Diffusion</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1.607389</v>
+        <v>1.94589</v>
       </c>
       <c r="E78" t="n">
-        <v>1.468671</v>
+        <v>1.816702</v>
       </c>
       <c r="F78" t="n">
-        <v>-0.1387179999999999</v>
+        <v>-0.1291879999999999</v>
       </c>
       <c r="G78" t="n">
-        <v>-8.630020486640129</v>
+        <v>-6.639018649563947</v>
       </c>
       <c r="H78" t="b">
         <v>0</v>
@@ -4122,30 +4122,30 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Metro</t>
+          <t>OnlineShop</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>CTGAN</t>
+          <t>TVAE</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>CTGAN</t>
+          <t>TVAE</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>0.431625</v>
+        <v>2.525588</v>
       </c>
       <c r="E79" t="n">
-        <v>0.399805</v>
+        <v>2.384212</v>
       </c>
       <c r="F79" t="n">
-        <v>-0.03181999999999996</v>
+        <v>-0.1413759999999997</v>
       </c>
       <c r="G79" t="n">
-        <v>-7.372140167969873</v>
+        <v>-5.597745950645938</v>
       </c>
       <c r="H79" t="b">
         <v>0</v>
@@ -4155,9 +4155,7 @@
           <t>Hungarian better (lower distance)</t>
         </is>
       </c>
-      <c r="J79" t="n">
-        <v>5000</v>
-      </c>
+      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
@@ -4169,30 +4167,30 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Metro</t>
+          <t>OnlineShop</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>TabDDPM</t>
+          <t>GaussianCopula</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>TabDDPM</t>
+          <t>Gaussian Copula</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>13.596022</v>
+        <v>1.722005</v>
       </c>
       <c r="E80" t="n">
-        <v>13.548747</v>
+        <v>1.587593</v>
       </c>
       <c r="F80" t="n">
-        <v>-0.04727499999999907</v>
+        <v>-0.134412</v>
       </c>
       <c r="G80" t="n">
-        <v>-0.3477119998776044</v>
+        <v>-7.805552248686849</v>
       </c>
       <c r="H80" t="b">
         <v>0</v>
@@ -4202,9 +4200,7 @@
           <t>Hungarian better (lower distance)</t>
         </is>
       </c>
-      <c r="J80" t="n">
-        <v>1000</v>
-      </c>
+      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
@@ -4216,30 +4212,30 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Metro</t>
+          <t>OnlineShop</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>CopulaGAN</t>
+          <t>WGAN_GP</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Copula GAN</t>
+          <t>WGAN-GP</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>0.587039</v>
+        <v>3.20519</v>
       </c>
       <c r="E81" t="n">
-        <v>0.482782</v>
+        <v>3.055943</v>
       </c>
       <c r="F81" t="n">
-        <v>-0.104257</v>
+        <v>-0.1492469999999999</v>
       </c>
       <c r="G81" t="n">
-        <v>-17.75980812177726</v>
+        <v>-4.65641662428748</v>
       </c>
       <c r="H81" t="b">
         <v>0</v>
@@ -4250,7 +4246,7 @@
         </is>
       </c>
       <c r="J81" t="n">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
@@ -4268,25 +4264,25 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>ForestDiffusion</t>
+          <t>CTABGAN</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Forest Diffusion</t>
+          <t>CTAB-GAN+</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1.94589</v>
+        <v>2.588096</v>
       </c>
       <c r="E82" t="n">
-        <v>1.816702</v>
+        <v>2.433242</v>
       </c>
       <c r="F82" t="n">
-        <v>-0.1291879999999999</v>
+        <v>-0.1548540000000003</v>
       </c>
       <c r="G82" t="n">
-        <v>-6.639018649563947</v>
+        <v>-5.983317465812716</v>
       </c>
       <c r="H82" t="b">
         <v>0</v>
@@ -4315,25 +4311,25 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>TVAE</t>
+          <t>CTGAN</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>TVAE</t>
+          <t>CTGAN</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>2.525588</v>
+        <v>1.712434</v>
       </c>
       <c r="E83" t="n">
-        <v>2.384212</v>
+        <v>1.567794</v>
       </c>
       <c r="F83" t="n">
-        <v>-0.1413759999999997</v>
+        <v>-0.1446400000000001</v>
       </c>
       <c r="G83" t="n">
-        <v>-5.597745950645938</v>
+        <v>-8.446456914543866</v>
       </c>
       <c r="H83" t="b">
         <v>0</v>
@@ -4360,25 +4356,25 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>GaussianCopula</t>
+          <t>TabDDPM</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Gaussian Copula</t>
+          <t>TabDDPM</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1.722005</v>
+        <v>5.801993</v>
       </c>
       <c r="E84" t="n">
-        <v>1.587593</v>
+        <v>5.638238</v>
       </c>
       <c r="F84" t="n">
-        <v>-0.134412</v>
+        <v>-0.1637550000000001</v>
       </c>
       <c r="G84" t="n">
-        <v>-7.805552248686849</v>
+        <v>-2.822392236598701</v>
       </c>
       <c r="H84" t="b">
         <v>0</v>
@@ -4388,7 +4384,9 @@
           <t>Hungarian better (lower distance)</t>
         </is>
       </c>
-      <c r="J84" t="inlineStr"/>
+      <c r="J84" t="n">
+        <v>1000</v>
+      </c>
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
@@ -4405,25 +4403,25 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>WGAN_GP</t>
+          <t>CopulaGAN</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>WGAN-GP</t>
+          <t>Copula GAN</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>3.20519</v>
+        <v>1.741369</v>
       </c>
       <c r="E85" t="n">
-        <v>3.055943</v>
+        <v>1.581511</v>
       </c>
       <c r="F85" t="n">
-        <v>-0.1492469999999999</v>
+        <v>-0.1598580000000001</v>
       </c>
       <c r="G85" t="n">
-        <v>-4.65641662428748</v>
+        <v>-9.180018709417709</v>
       </c>
       <c r="H85" t="b">
         <v>0</v>
@@ -4433,9 +4431,7 @@
           <t>Hungarian better (lower distance)</t>
         </is>
       </c>
-      <c r="J85" t="n">
-        <v>1000</v>
-      </c>
+      <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
@@ -4447,30 +4443,30 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>OnlineShop</t>
+          <t>AirQuality</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>CTABGAN</t>
+          <t>ForestDiffusion</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>CTAB-GAN+</t>
+          <t>Forest Diffusion</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>2.588096</v>
+        <v>1.7287</v>
       </c>
       <c r="E86" t="n">
-        <v>2.433242</v>
+        <v>1.6389</v>
       </c>
       <c r="F86" t="n">
-        <v>-0.1548540000000003</v>
+        <v>-0.08979999999999988</v>
       </c>
       <c r="G86" t="n">
-        <v>-5.983317465812716</v>
+        <v>-5.19465494302076</v>
       </c>
       <c r="H86" t="b">
         <v>0</v>
@@ -4494,30 +4490,30 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>OnlineShop</t>
+          <t>AirQuality</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>CTGAN</t>
+          <t>TVAE</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>CTGAN</t>
+          <t>TVAE</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1.712434</v>
+        <v>53.42266</v>
       </c>
       <c r="E87" t="n">
-        <v>1.567794</v>
+        <v>20.605003</v>
       </c>
       <c r="F87" t="n">
-        <v>-0.1446400000000001</v>
+        <v>-32.817657</v>
       </c>
       <c r="G87" t="n">
-        <v>-8.446456914543866</v>
+        <v>-61.43021893705779</v>
       </c>
       <c r="H87" t="b">
         <v>0</v>
@@ -4527,7 +4523,9 @@
           <t>Hungarian better (lower distance)</t>
         </is>
       </c>
-      <c r="J87" t="inlineStr"/>
+      <c r="J87" t="n">
+        <v>1000</v>
+      </c>
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr">
@@ -4539,30 +4537,30 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>OnlineShop</t>
+          <t>AirQuality</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>TabDDPM</t>
+          <t>GaussianCopula</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>TabDDPM</t>
+          <t>Gaussian Copula</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>5.801993</v>
+        <v>28.73888</v>
       </c>
       <c r="E88" t="n">
-        <v>5.638238</v>
+        <v>18.531944</v>
       </c>
       <c r="F88" t="n">
-        <v>-0.1637550000000001</v>
+        <v>-10.206936</v>
       </c>
       <c r="G88" t="n">
-        <v>-2.822392236598701</v>
+        <v>-35.51612310570211</v>
       </c>
       <c r="H88" t="b">
         <v>0</v>
@@ -4586,30 +4584,30 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>OnlineShop</t>
+          <t>AirQuality</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>CopulaGAN</t>
+          <t>WGAN_GP</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Copula GAN</t>
+          <t>WGAN-GP</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1.741369</v>
+        <v>4.9184</v>
       </c>
       <c r="E89" t="n">
-        <v>1.581511</v>
+        <v>4.6189</v>
       </c>
       <c r="F89" t="n">
-        <v>-0.1598580000000001</v>
+        <v>-0.2995000000000001</v>
       </c>
       <c r="G89" t="n">
-        <v>-9.180018709417709</v>
+        <v>-6.089378659726743</v>
       </c>
       <c r="H89" t="b">
         <v>0</v>
@@ -4636,25 +4634,25 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>ForestDiffusion</t>
+          <t>CTABGAN</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Forest Diffusion</t>
+          <t>CTAB-GAN+</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1.7287</v>
+        <v>9.283799999999999</v>
       </c>
       <c r="E90" t="n">
-        <v>1.6389</v>
+        <v>9.02</v>
       </c>
       <c r="F90" t="n">
-        <v>-0.08979999999999988</v>
+        <v>-0.2637999999999998</v>
       </c>
       <c r="G90" t="n">
-        <v>-5.19465494302076</v>
+        <v>-2.841508864904455</v>
       </c>
       <c r="H90" t="b">
         <v>0</v>
@@ -4664,9 +4662,7 @@
           <t>Hungarian better (lower distance)</t>
         </is>
       </c>
-      <c r="J90" t="n">
-        <v>1000</v>
-      </c>
+      <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr">
@@ -4683,25 +4679,25 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>TVAE</t>
+          <t>TabDDPM</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>TVAE</t>
+          <t>TabDDPM</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>53.42266</v>
+        <v>6.392</v>
       </c>
       <c r="E91" t="n">
-        <v>20.605003</v>
+        <v>6.1055</v>
       </c>
       <c r="F91" t="n">
-        <v>-32.817657</v>
+        <v>-0.2865000000000002</v>
       </c>
       <c r="G91" t="n">
-        <v>-61.43021893705779</v>
+        <v>-4.482165206508138</v>
       </c>
       <c r="H91" t="b">
         <v>0</v>
@@ -4725,30 +4721,30 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>AirQuality</t>
+          <t>Concrete</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>GaussianCopula</t>
+          <t>ForestDiffusion</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Gaussian Copula</t>
+          <t>Forest Diffusion</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>28.73888</v>
+        <v>0.9112</v>
       </c>
       <c r="E92" t="n">
-        <v>18.531944</v>
+        <v>0.8489</v>
       </c>
       <c r="F92" t="n">
-        <v>-10.206936</v>
+        <v>-0.06230000000000002</v>
       </c>
       <c r="G92" t="n">
-        <v>-35.51612310570211</v>
+        <v>-6.837137840210714</v>
       </c>
       <c r="H92" t="b">
         <v>0</v>
@@ -4772,30 +4768,30 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>AirQuality</t>
+          <t>Concrete</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>WGAN_GP</t>
+          <t>TVAE</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>WGAN-GP</t>
+          <t>TVAE</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>4.9184</v>
+        <v>3.345275</v>
       </c>
       <c r="E93" t="n">
-        <v>4.6189</v>
+        <v>3.145877</v>
       </c>
       <c r="F93" t="n">
-        <v>-0.2995000000000001</v>
+        <v>-0.199398</v>
       </c>
       <c r="G93" t="n">
-        <v>-6.089378659726743</v>
+        <v>-5.960586199938719</v>
       </c>
       <c r="H93" t="b">
         <v>0</v>
@@ -4805,7 +4801,9 @@
           <t>Hungarian better (lower distance)</t>
         </is>
       </c>
-      <c r="J93" t="inlineStr"/>
+      <c r="J93" t="n">
+        <v>1000</v>
+      </c>
       <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
@@ -4817,30 +4815,30 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>AirQuality</t>
+          <t>Concrete</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>CTABGAN</t>
+          <t>GaussianCopula</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>CTAB-GAN+</t>
+          <t>Gaussian Copula</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>9.283799999999999</v>
+        <v>3.985879</v>
       </c>
       <c r="E94" t="n">
-        <v>9.02</v>
+        <v>3.685769</v>
       </c>
       <c r="F94" t="n">
-        <v>-0.2637999999999998</v>
+        <v>-0.3001100000000001</v>
       </c>
       <c r="G94" t="n">
-        <v>-2.841508864904455</v>
+        <v>-7.529330418710655</v>
       </c>
       <c r="H94" t="b">
         <v>0</v>
@@ -4850,7 +4848,9 @@
           <t>Hungarian better (lower distance)</t>
         </is>
       </c>
-      <c r="J94" t="inlineStr"/>
+      <c r="J94" t="n">
+        <v>1000</v>
+      </c>
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
@@ -4862,30 +4862,30 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>AirQuality</t>
+          <t>Concrete</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>CTGAN</t>
+          <t>WGAN_GP</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>CTGAN</t>
+          <t>WGAN-GP</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>15.87754573663957</v>
+        <v>3.6759</v>
       </c>
       <c r="E95" t="n">
-        <v>15.58214745304394</v>
+        <v>3.3891</v>
       </c>
       <c r="F95" t="n">
-        <v>-0.2953982835956328</v>
+        <v>-0.2867999999999999</v>
       </c>
       <c r="G95" t="n">
-        <v>-1.860478240752043</v>
+        <v>-7.802170896923201</v>
       </c>
       <c r="H95" t="b">
         <v>0</v>
@@ -4909,30 +4909,30 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>AirQuality</t>
+          <t>Concrete</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>TabDDPM</t>
+          <t>CTABGAN</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>TabDDPM</t>
+          <t>CTAB-GAN+</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>6.392</v>
+        <v>3.3377</v>
       </c>
       <c r="E96" t="n">
-        <v>6.1055</v>
+        <v>3.1203</v>
       </c>
       <c r="F96" t="n">
-        <v>-0.2865000000000002</v>
+        <v>-0.2174</v>
       </c>
       <c r="G96" t="n">
-        <v>-4.482165206508138</v>
+        <v>-6.513467357761334</v>
       </c>
       <c r="H96" t="b">
         <v>0</v>
@@ -4956,30 +4956,30 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>AirQuality</t>
+          <t>Concrete</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>CopulaGAN</t>
+          <t>CTGAN</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Copula GAN</t>
+          <t>CTGAN</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>17.04914586325495</v>
+        <v>5.242352</v>
       </c>
       <c r="E97" t="n">
-        <v>16.7797488635705</v>
+        <v>5.018745</v>
       </c>
       <c r="F97" t="n">
-        <v>-0.2693969996844494</v>
+        <v>-0.2236070000000003</v>
       </c>
       <c r="G97" t="n">
-        <v>-1.580120211564765</v>
+        <v>-4.265394616767442</v>
       </c>
       <c r="H97" t="b">
         <v>0</v>
@@ -5008,25 +5008,25 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ForestDiffusion</t>
+          <t>TabDDPM</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Forest Diffusion</t>
+          <t>TabDDPM</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>0.9112</v>
+        <v>1.7551</v>
       </c>
       <c r="E98" t="n">
-        <v>0.8489</v>
+        <v>1.6227</v>
       </c>
       <c r="F98" t="n">
-        <v>-0.06230000000000002</v>
+        <v>-0.1324000000000001</v>
       </c>
       <c r="G98" t="n">
-        <v>-6.837137840210714</v>
+        <v>-7.543729702011285</v>
       </c>
       <c r="H98" t="b">
         <v>0</v>
@@ -5055,25 +5055,25 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>TVAE</t>
+          <t>CopulaGAN</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>TVAE</t>
+          <t>Copula GAN</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>3.345275</v>
+        <v>6.754965</v>
       </c>
       <c r="E99" t="n">
-        <v>3.145877</v>
+        <v>6.507187</v>
       </c>
       <c r="F99" t="n">
-        <v>-0.199398</v>
+        <v>-0.2477780000000003</v>
       </c>
       <c r="G99" t="n">
-        <v>-5.960586199938719</v>
+        <v>-3.668087103338067</v>
       </c>
       <c r="H99" t="b">
         <v>0</v>
@@ -5097,30 +5097,30 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Concrete</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>GaussianCopula</t>
+          <t>ForestDiffusion</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Gaussian Copula</t>
+          <t>Forest Diffusion</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>3.985879</v>
+        <v>41.2109</v>
       </c>
       <c r="E100" t="n">
-        <v>3.685769</v>
+        <v>41.2089</v>
       </c>
       <c r="F100" t="n">
-        <v>-0.3001100000000001</v>
+        <v>-0.002000000000002444</v>
       </c>
       <c r="G100" t="n">
-        <v>-7.529330418710655</v>
+        <v>-0.004853084984803642</v>
       </c>
       <c r="H100" t="b">
         <v>0</v>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="J100" t="n">
-        <v>1000</v>
+        <v>768</v>
       </c>
       <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr"/>
@@ -5144,30 +5144,30 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Concrete</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>WGAN_GP</t>
+          <t>TVAE</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>WGAN-GP</t>
+          <t>TVAE</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>3.6759</v>
+        <v>18868.031041</v>
       </c>
       <c r="E101" t="n">
-        <v>3.3891</v>
+        <v>18868.030988</v>
       </c>
       <c r="F101" t="n">
-        <v>-0.2867999999999999</v>
+        <v>-5.299999975250103e-05</v>
       </c>
       <c r="G101" t="n">
-        <v>-7.802170896923201</v>
+        <v>-2.808984129681188e-07</v>
       </c>
       <c r="H101" t="b">
         <v>0</v>
@@ -5178,7 +5178,7 @@
         </is>
       </c>
       <c r="J101" t="n">
-        <v>1000</v>
+        <v>768</v>
       </c>
       <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr"/>
@@ -5191,30 +5191,30 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Concrete</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>CTABGAN</t>
+          <t>GaussianCopula</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>CTAB-GAN+</t>
+          <t>Gaussian Copula</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>3.3377</v>
+        <v>21169.768599</v>
       </c>
       <c r="E102" t="n">
-        <v>3.1203</v>
+        <v>21169.768524</v>
       </c>
       <c r="F102" t="n">
-        <v>-0.2174</v>
+        <v>-7.499999992433004e-05</v>
       </c>
       <c r="G102" t="n">
-        <v>-6.513467357761334</v>
+        <v>-3.542787894614627e-07</v>
       </c>
       <c r="H102" t="b">
         <v>0</v>
@@ -5225,7 +5225,7 @@
         </is>
       </c>
       <c r="J102" t="n">
-        <v>1000</v>
+        <v>768</v>
       </c>
       <c r="K102" t="inlineStr"/>
       <c r="L102" t="inlineStr"/>
@@ -5238,41 +5238,41 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Concrete</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>CTGAN</t>
+          <t>WGAN_GP</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>CTGAN</t>
+          <t>WGAN-GP</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>5.242352</v>
+        <v>23616.3467</v>
       </c>
       <c r="E103" t="n">
-        <v>5.018745</v>
+        <v>23616.3467</v>
       </c>
       <c r="F103" t="n">
-        <v>-0.2236070000000003</v>
+        <v>0</v>
       </c>
       <c r="G103" t="n">
-        <v>-4.265394616767442</v>
+        <v>0</v>
       </c>
       <c r="H103" t="b">
         <v>0</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Hungarian better (lower distance)</t>
+          <t>Negligible / tie</t>
         </is>
       </c>
       <c r="J103" t="n">
-        <v>1000</v>
+        <v>768</v>
       </c>
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr"/>
@@ -5285,41 +5285,41 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Concrete</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>TabDDPM</t>
+          <t>CTABGAN</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>TabDDPM</t>
+          <t>CTAB-GAN+</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>1.7551</v>
+        <v>21021.1892</v>
       </c>
       <c r="E104" t="n">
-        <v>1.6227</v>
+        <v>21021.1892</v>
       </c>
       <c r="F104" t="n">
-        <v>-0.1324000000000001</v>
+        <v>0</v>
       </c>
       <c r="G104" t="n">
-        <v>-7.543729702011285</v>
+        <v>0</v>
       </c>
       <c r="H104" t="b">
         <v>0</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Hungarian better (lower distance)</t>
+          <t>Negligible / tie</t>
         </is>
       </c>
       <c r="J104" t="n">
-        <v>1000</v>
+        <v>768</v>
       </c>
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr"/>
@@ -5332,30 +5332,30 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Concrete</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>CopulaGAN</t>
+          <t>CTGAN</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Copula GAN</t>
+          <t>CTGAN</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>6.754965</v>
+        <v>45637.724946</v>
       </c>
       <c r="E105" t="n">
-        <v>6.507187</v>
+        <v>45637.724902</v>
       </c>
       <c r="F105" t="n">
-        <v>-0.2477780000000003</v>
+        <v>-4.400000034365803e-05</v>
       </c>
       <c r="G105" t="n">
-        <v>-3.668087103338067</v>
+        <v>-9.641146747722464e-08</v>
       </c>
       <c r="H105" t="b">
         <v>0</v>
@@ -5366,7 +5366,7 @@
         </is>
       </c>
       <c r="J105" t="n">
-        <v>1000</v>
+        <v>768</v>
       </c>
       <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr"/>
@@ -5384,32 +5384,32 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>ForestDiffusion</t>
+          <t>TabDDPM</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Forest Diffusion</t>
+          <t>TabDDPM</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>41.2109</v>
+        <v>15946.4815</v>
       </c>
       <c r="E106" t="n">
-        <v>41.2089</v>
+        <v>15946.4815</v>
       </c>
       <c r="F106" t="n">
-        <v>-0.002000000000002444</v>
+        <v>0</v>
       </c>
       <c r="G106" t="n">
-        <v>-0.004853084984803642</v>
+        <v>0</v>
       </c>
       <c r="H106" t="b">
         <v>0</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Hungarian better (lower distance)</t>
+          <t>Negligible / tie</t>
         </is>
       </c>
       <c r="J106" t="n">
@@ -5431,25 +5431,25 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>TVAE</t>
+          <t>CopulaGAN</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>TVAE</t>
+          <t>Copula GAN</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>18868.031041</v>
+        <v>51117.382605</v>
       </c>
       <c r="E107" t="n">
-        <v>18868.030988</v>
+        <v>51117.382555</v>
       </c>
       <c r="F107" t="n">
-        <v>-5.299999975250103e-05</v>
+        <v>-5.000000237487257e-05</v>
       </c>
       <c r="G107" t="n">
-        <v>-2.808984129681188e-07</v>
+        <v>-9.781408950696522e-08</v>
       </c>
       <c r="H107" t="b">
         <v>0</v>
@@ -5473,30 +5473,30 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>RealEstate</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>GaussianCopula</t>
+          <t>ForestDiffusion</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Gaussian Copula</t>
+          <t>Forest Diffusion</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>21169.768599</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="E108" t="n">
-        <v>21169.768524</v>
+        <v>0.0771</v>
       </c>
       <c r="F108" t="n">
-        <v>-7.499999992433004e-05</v>
+        <v>-0.0001999999999999919</v>
       </c>
       <c r="G108" t="n">
-        <v>-3.542787894614627e-07</v>
+        <v>-0.2587322121604034</v>
       </c>
       <c r="H108" t="b">
         <v>0</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="J108" t="n">
-        <v>768</v>
+        <v>414</v>
       </c>
       <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr"/>
@@ -5520,41 +5520,41 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>RealEstate</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>WGAN_GP</t>
+          <t>TVAE</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>WGAN-GP</t>
+          <t>TVAE</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>23616.3467</v>
+        <v>16693.918272</v>
       </c>
       <c r="E109" t="n">
-        <v>23616.3467</v>
+        <v>16693.789109</v>
       </c>
       <c r="F109" t="n">
-        <v>0</v>
+        <v>-0.1291629999977886</v>
       </c>
       <c r="G109" t="n">
-        <v>0</v>
+        <v>-0.0007737129048632531</v>
       </c>
       <c r="H109" t="b">
         <v>0</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Negligible / tie</t>
+          <t>Hungarian better (lower distance)</t>
         </is>
       </c>
       <c r="J109" t="n">
-        <v>768</v>
+        <v>414</v>
       </c>
       <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr"/>
@@ -5567,41 +5567,41 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>RealEstate</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>CTABGAN</t>
+          <t>GaussianCopula</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>CTAB-GAN+</t>
+          <t>Gaussian Copula</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>21021.1892</v>
+        <v>16693.682733</v>
       </c>
       <c r="E110" t="n">
-        <v>21021.1892</v>
+        <v>16693.553751</v>
       </c>
       <c r="F110" t="n">
-        <v>0</v>
+        <v>-0.1289820000019972</v>
       </c>
       <c r="G110" t="n">
-        <v>0</v>
+        <v>-0.0007726395790847645</v>
       </c>
       <c r="H110" t="b">
         <v>0</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Negligible / tie</t>
+          <t>Hungarian better (lower distance)</t>
         </is>
       </c>
       <c r="J110" t="n">
-        <v>768</v>
+        <v>414</v>
       </c>
       <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr"/>
@@ -5614,30 +5614,30 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>RealEstate</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>CTGAN</t>
+          <t>WGAN_GP</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>CTGAN</t>
+          <t>WGAN-GP</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>45637.724946</v>
+        <v>1.4639</v>
       </c>
       <c r="E111" t="n">
-        <v>45637.724902</v>
+        <v>1.3965</v>
       </c>
       <c r="F111" t="n">
-        <v>-4.400000034365803e-05</v>
+        <v>-0.0673999999999999</v>
       </c>
       <c r="G111" t="n">
-        <v>-9.641146747722464e-08</v>
+        <v>-4.604139627023697</v>
       </c>
       <c r="H111" t="b">
         <v>0</v>
@@ -5648,7 +5648,7 @@
         </is>
       </c>
       <c r="J111" t="n">
-        <v>768</v>
+        <v>414</v>
       </c>
       <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr"/>
@@ -5661,41 +5661,41 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>RealEstate</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>TabDDPM</t>
+          <t>CTABGAN</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>TabDDPM</t>
+          <t>CTAB-GAN+</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>15946.4815</v>
+        <v>0.9013</v>
       </c>
       <c r="E112" t="n">
-        <v>15946.4815</v>
+        <v>0.8723</v>
       </c>
       <c r="F112" t="n">
-        <v>0</v>
+        <v>-0.02900000000000003</v>
       </c>
       <c r="G112" t="n">
-        <v>0</v>
+        <v>-3.217574614445804</v>
       </c>
       <c r="H112" t="b">
         <v>0</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Negligible / tie</t>
+          <t>Hungarian better (lower distance)</t>
         </is>
       </c>
       <c r="J112" t="n">
-        <v>768</v>
+        <v>414</v>
       </c>
       <c r="K112" t="inlineStr"/>
       <c r="L112" t="inlineStr"/>
@@ -5708,30 +5708,30 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>RealEstate</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>CopulaGAN</t>
+          <t>CTGAN</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Copula GAN</t>
+          <t>CTGAN</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>51117.382605</v>
+        <v>16692.881415</v>
       </c>
       <c r="E113" t="n">
-        <v>51117.382555</v>
+        <v>16692.752234</v>
       </c>
       <c r="F113" t="n">
-        <v>-5.000000237487257e-05</v>
+        <v>-0.1291810000002442</v>
       </c>
       <c r="G113" t="n">
-        <v>-9.781408950696522e-08</v>
+        <v>-0.0007738687934616484</v>
       </c>
       <c r="H113" t="b">
         <v>0</v>
@@ -5742,7 +5742,7 @@
         </is>
       </c>
       <c r="J113" t="n">
-        <v>768</v>
+        <v>414</v>
       </c>
       <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr"/>
@@ -5760,25 +5760,25 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>ForestDiffusion</t>
+          <t>TabDDPM</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Forest Diffusion</t>
+          <t>TabDDPM</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>0.07729999999999999</v>
+        <v>0.9375</v>
       </c>
       <c r="E114" t="n">
-        <v>0.0771</v>
+        <v>0.8743</v>
       </c>
       <c r="F114" t="n">
-        <v>-0.0001999999999999919</v>
+        <v>-0.06320000000000003</v>
       </c>
       <c r="G114" t="n">
-        <v>-0.2587322121604034</v>
+        <v>-6.741333333333338</v>
       </c>
       <c r="H114" t="b">
         <v>0</v>
@@ -5807,25 +5807,25 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>TVAE</t>
+          <t>CopulaGAN</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>TVAE</t>
+          <t>Copula GAN</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>16693.918272</v>
+        <v>16693.963602</v>
       </c>
       <c r="E115" t="n">
-        <v>16693.789109</v>
+        <v>16693.834433</v>
       </c>
       <c r="F115" t="n">
-        <v>-0.1291629999977886</v>
+        <v>-0.1291689999998198</v>
       </c>
       <c r="G115" t="n">
-        <v>-0.0007737129048632531</v>
+        <v>-0.000773746745106985</v>
       </c>
       <c r="H115" t="b">
         <v>0</v>
@@ -5841,288 +5841,6 @@
       <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr">
-        <is>
-          <t>Not available in extracted results</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>RealEstate</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>GaussianCopula</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Gaussian Copula</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>16693.682733</v>
-      </c>
-      <c r="E116" t="n">
-        <v>16693.553751</v>
-      </c>
-      <c r="F116" t="n">
-        <v>-0.1289820000019972</v>
-      </c>
-      <c r="G116" t="n">
-        <v>-0.0007726395790847645</v>
-      </c>
-      <c r="H116" t="b">
-        <v>0</v>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>Hungarian better (lower distance)</t>
-        </is>
-      </c>
-      <c r="J116" t="n">
-        <v>414</v>
-      </c>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>Not available in extracted results</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>RealEstate</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>WGAN_GP</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>WGAN-GP</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>1.4639</v>
-      </c>
-      <c r="E117" t="n">
-        <v>1.3965</v>
-      </c>
-      <c r="F117" t="n">
-        <v>-0.0673999999999999</v>
-      </c>
-      <c r="G117" t="n">
-        <v>-4.604139627023697</v>
-      </c>
-      <c r="H117" t="b">
-        <v>0</v>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>Hungarian better (lower distance)</t>
-        </is>
-      </c>
-      <c r="J117" t="n">
-        <v>414</v>
-      </c>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>Not available in extracted results</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>RealEstate</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>CTABGAN</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>CTAB-GAN+</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>0.9013</v>
-      </c>
-      <c r="E118" t="n">
-        <v>0.8723</v>
-      </c>
-      <c r="F118" t="n">
-        <v>-0.02900000000000003</v>
-      </c>
-      <c r="G118" t="n">
-        <v>-3.217574614445804</v>
-      </c>
-      <c r="H118" t="b">
-        <v>0</v>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>Hungarian better (lower distance)</t>
-        </is>
-      </c>
-      <c r="J118" t="n">
-        <v>414</v>
-      </c>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>Not available in extracted results</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>RealEstate</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>CTGAN</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>CTGAN</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>16692.881415</v>
-      </c>
-      <c r="E119" t="n">
-        <v>16692.752234</v>
-      </c>
-      <c r="F119" t="n">
-        <v>-0.1291810000002442</v>
-      </c>
-      <c r="G119" t="n">
-        <v>-0.0007738687934616484</v>
-      </c>
-      <c r="H119" t="b">
-        <v>0</v>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>Hungarian better (lower distance)</t>
-        </is>
-      </c>
-      <c r="J119" t="n">
-        <v>414</v>
-      </c>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>Not available in extracted results</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>RealEstate</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>TabDDPM</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>TabDDPM</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>0.9375</v>
-      </c>
-      <c r="E120" t="n">
-        <v>0.8743</v>
-      </c>
-      <c r="F120" t="n">
-        <v>-0.06320000000000003</v>
-      </c>
-      <c r="G120" t="n">
-        <v>-6.741333333333338</v>
-      </c>
-      <c r="H120" t="b">
-        <v>0</v>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>Hungarian better (lower distance)</t>
-        </is>
-      </c>
-      <c r="J120" t="n">
-        <v>414</v>
-      </c>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>Not available in extracted results</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>RealEstate</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>CopulaGAN</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Copula GAN</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>16693.963602</v>
-      </c>
-      <c r="E121" t="n">
-        <v>16693.834433</v>
-      </c>
-      <c r="F121" t="n">
-        <v>-0.1291689999998198</v>
-      </c>
-      <c r="G121" t="n">
-        <v>-0.000773746745106985</v>
-      </c>
-      <c r="H121" t="b">
-        <v>0</v>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>Hungarian better (lower distance)</t>
-        </is>
-      </c>
-      <c r="J121" t="n">
-        <v>414</v>
-      </c>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
         <is>
           <t>Not available in extracted results</t>
         </is>
@@ -6331,22 +6049,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C7" t="n">
-        <v>3.18677296584983</v>
+        <v>3.5259</v>
       </c>
       <c r="D7" t="n">
-        <v>2.890093722731807</v>
+        <v>3.302575</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2966792431180231</v>
+        <v>-0.2233250000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1367471562866815</v>
+        <v>0.08840932737368087</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.2877500000000002</v>
+        <v>-0.2521</v>
       </c>
       <c r="H7" t="n">
         <v>100</v>
@@ -6499,22 +6217,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>17.17639144998682</v>
+        <v>17.41407333333333</v>
       </c>
       <c r="D13" t="n">
-        <v>11.6102679145768</v>
+        <v>10.08670783333333</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.56612353541001</v>
+        <v>-7.327365499999999</v>
       </c>
       <c r="F13" t="n">
-        <v>11.54949334482794</v>
+        <v>13.10944605568217</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.2909491417978165</v>
+        <v>-0.2930000000000001</v>
       </c>
       <c r="H13" t="n">
         <v>100</v>
@@ -6705,25 +6423,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C3" t="n">
-        <v>2391.542782609838</v>
+        <v>2562.185114857143</v>
       </c>
       <c r="D3" t="n">
-        <v>2389.263592576157</v>
+        <v>2559.777961857143</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.279190033680912</v>
+        <v>-2.407152999999826</v>
       </c>
       <c r="F3" t="n">
-        <v>8.452418160755425</v>
+        <v>8.756397965718179</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.1413759999999997</v>
+        <v>-0.1352694999988941</v>
       </c>
       <c r="H3" t="n">
-        <v>86.66666666666667</v>
+        <v>85.71428571428571</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -6738,25 +6456,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C4" t="n">
-        <v>2549.061096494515</v>
+        <v>2730.982060785714</v>
       </c>
       <c r="D4" t="n">
-        <v>2548.259643721199</v>
+        <v>2730.134539</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.8014527733160101</v>
+        <v>-0.8475217857144232</v>
       </c>
       <c r="F4" t="n">
-        <v>2.611169436185693</v>
+        <v>2.703405078256759</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.144391</v>
+        <v>-0.1415509999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>93.33333333333333</v>
+        <v>92.85714285714286</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -6837,25 +6555,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C7" t="n">
-        <v>4191.713807989657</v>
+        <v>4835.102192538461</v>
       </c>
       <c r="D7" t="n">
-        <v>4191.588570994254</v>
+        <v>4835.011534</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1252369954025745</v>
+        <v>-0.09065853846158133</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3208004624114607</v>
+        <v>0.3314414587828434</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.2236070000000003</v>
+        <v>-0.1446400000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>93.33333333333333</v>
+        <v>92.30769230769231</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -6903,25 +6621,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C9" t="n">
-        <v>4559.27508912777</v>
+        <v>5259.146569692308</v>
       </c>
       <c r="D9" t="n">
-        <v>4559.128942848288</v>
+        <v>5259.031842461539</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1461462794822696</v>
+        <v>-0.1147272307693983</v>
       </c>
       <c r="F9" t="n">
-        <v>0.303774030532835</v>
+        <v>0.3139188068364924</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.2122929999999998</v>
+        <v>-0.1598580000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>93.33333333333333</v>
+        <v>92.30769230769231</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -7032,25 +6750,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="D2" t="n">
-        <v>2228.795533469389</v>
+        <v>2345.711813517544</v>
       </c>
       <c r="E2" t="n">
-        <v>2228.311833309154</v>
+        <v>2345.220593429824</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.4837001602352213</v>
+        <v>-0.4912200877193183</v>
       </c>
       <c r="G2" t="n">
-        <v>3.121977584066546</v>
+        <v>3.203508345872733</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.1392589999999998</v>
+        <v>-0.133406</v>
       </c>
       <c r="I2" t="n">
-        <v>93.33333333333333</v>
+        <v>92.98245614035088</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -7058,13 +6776,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>6435</v>
+        <v>5772</v>
       </c>
       <c r="L2" t="n">
-        <v>2.438031880918587e-16</v>
+        <v>2.28491228901825e-15</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7727272727272727</v>
+        <v>0.7610983981693364</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -7072,7 +6790,7 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>2.438031880918587e-16</v>
+        <v>2.28491228901825e-15</v>
       </c>
     </row>
     <row r="3">
@@ -7142,25 +6860,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D4" t="n">
-        <v>2391.542782609838</v>
+        <v>2562.185114857143</v>
       </c>
       <c r="E4" t="n">
-        <v>2389.263592576157</v>
+        <v>2559.777961857143</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.279190033680912</v>
+        <v>-2.407152999999826</v>
       </c>
       <c r="G4" t="n">
-        <v>8.452418160755425</v>
+        <v>8.756397965718179</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.1413759999999997</v>
+        <v>-0.1352694999988941</v>
       </c>
       <c r="I4" t="n">
-        <v>86.66666666666667</v>
+        <v>85.71428571428571</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -7168,13 +6886,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="L4" t="n">
-        <v>0.005126953125</v>
+        <v>0.00830078125</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7333333333333334</v>
+        <v>0.7142857142857142</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -7182,7 +6900,7 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>0.013427734375</v>
+        <v>0.02490234375</v>
       </c>
     </row>
     <row r="5">
@@ -7197,25 +6915,25 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D5" t="n">
-        <v>2549.061096494515</v>
+        <v>2730.982060785714</v>
       </c>
       <c r="E5" t="n">
-        <v>2548.259643721199</v>
+        <v>2730.134539</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.8014527733160101</v>
+        <v>-0.8475217857144232</v>
       </c>
       <c r="G5" t="n">
-        <v>2.611169436185693</v>
+        <v>2.703405078256759</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.144391</v>
+        <v>-0.1415509999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>93.33333333333333</v>
+        <v>92.85714285714286</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -7223,13 +6941,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="L5" t="n">
-        <v>0.00335693359375</v>
+        <v>0.00537109375</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7666666666666666</v>
+        <v>0.7523809523809524</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -7237,7 +6955,7 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>0.013427734375</v>
+        <v>0.021484375</v>
       </c>
     </row>
     <row r="6">
@@ -7362,25 +7080,25 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D8" t="n">
-        <v>4191.713807989657</v>
+        <v>4835.102192538461</v>
       </c>
       <c r="E8" t="n">
-        <v>4191.588570994254</v>
+        <v>4835.011534</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1252369954025745</v>
+        <v>-0.09065853846158135</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3208004624114607</v>
+        <v>0.3314414587828435</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2236070000000003</v>
+        <v>-0.1446400000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>93.33333333333333</v>
+        <v>92.30769230769231</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -7388,13 +7106,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="L8" t="n">
-        <v>0.004180908203125</v>
+        <v>0.0107421875</v>
       </c>
       <c r="M8" t="n">
-        <v>0.75</v>
+        <v>0.7142857142857142</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -7402,7 +7120,7 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>0.013427734375</v>
+        <v>0.02490234375</v>
       </c>
     </row>
     <row r="9">
@@ -7472,25 +7190,25 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D10" t="n">
-        <v>4559.27508912777</v>
+        <v>5259.146569692308</v>
       </c>
       <c r="E10" t="n">
-        <v>4559.128942848287</v>
+        <v>5259.031842461539</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1461462794822696</v>
+        <v>-0.1147272307693983</v>
       </c>
       <c r="G10" t="n">
-        <v>0.303774030532835</v>
+        <v>0.3139188068364924</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2122929999999998</v>
+        <v>-0.1598580000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>93.33333333333333</v>
+        <v>92.30769230769231</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -7498,13 +7216,13 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="L10" t="n">
-        <v>0.004180908203125</v>
+        <v>0.0107421875</v>
       </c>
       <c r="M10" t="n">
-        <v>0.75</v>
+        <v>0.7142857142857142</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -7512,7 +7230,7 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>0.013427734375</v>
+        <v>0.02490234375</v>
       </c>
     </row>
     <row r="11">
@@ -7802,22 +7520,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>3.18677296584983</v>
+        <v>3.5259</v>
       </c>
       <c r="E16" t="n">
-        <v>2.890093722731807</v>
+        <v>3.302575</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2966792431180231</v>
+        <v>-0.2233250000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1367471562866815</v>
+        <v>0.08840932737368087</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.2877500000000002</v>
+        <v>-0.2521</v>
       </c>
       <c r="I16" t="n">
         <v>100</v>
@@ -7828,10 +7546,10 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="L16" t="n">
-        <v>0.00390625</v>
+        <v>0.0625</v>
       </c>
       <c r="M16" t="n">
         <v>1</v>
@@ -7842,7 +7560,7 @@
         </is>
       </c>
       <c r="O16" t="n">
-        <v>0.05859375</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="17">
@@ -8132,22 +7850,22 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D22" t="n">
-        <v>17.17639144998682</v>
+        <v>17.41407333333333</v>
       </c>
       <c r="E22" t="n">
-        <v>11.6102679145768</v>
+        <v>10.08670783333333</v>
       </c>
       <c r="F22" t="n">
-        <v>-5.56612353541001</v>
+        <v>-7.327365499999999</v>
       </c>
       <c r="G22" t="n">
-        <v>11.54949334482794</v>
+        <v>13.10944605568216</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.2909491417978165</v>
+        <v>-0.2930000000000001</v>
       </c>
       <c r="I22" t="n">
         <v>100</v>
@@ -8158,10 +7876,10 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="L22" t="n">
-        <v>0.00390625</v>
+        <v>0.015625</v>
       </c>
       <c r="M22" t="n">
         <v>1</v>
@@ -8172,7 +7890,7 @@
         </is>
       </c>
       <c r="O22" t="n">
-        <v>0.05859375</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="23">
@@ -8282,7 +8000,7 @@
         </is>
       </c>
       <c r="O24" t="n">
-        <v>0.0625</v>
+        <v>0.09375</v>
       </c>
     </row>
     <row r="25">
@@ -8351,9 +8069,129 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>generator</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Wine</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>CTGAN</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>incomplete Mahalanobis methods available: ['Hungarian', 'One-to-One Greedy']</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Wine</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CopulaGAN</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>incomplete Mahalanobis methods available: ['Hungarian', 'One-to-One Greedy']</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Wine</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>TVAE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>incomplete Mahalanobis methods available: ['Hungarian', 'One-to-One Greedy']</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Wine</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>GaussianCopula</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>incomplete Mahalanobis methods available: ['Hungarian', 'One-to-One Greedy']</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AirQuality</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CTGAN</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>incomplete Mahalanobis methods available: ['Hungarian', 'One-to-One Greedy']</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AirQuality</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CopulaGAN</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>incomplete Mahalanobis methods available: ['Hungarian', 'One-to-One Greedy']</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8422,7 +8260,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>120</v>
+        <v>114</v>
       </c>
     </row>
     <row r="6">
@@ -8432,7 +8270,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
